--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK10"/>
+  <dimension ref="A1:AK13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45908.5</v>
+        <v>45908.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45908.5625</v>
+        <v>45908.52083333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45908.64583333334</v>
+        <v>45908.52083333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45908.8125</v>
+        <v>45908.52083333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45908.83333333334</v>
+        <v>45908.5625</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45908.83333333334</v>
+        <v>45908.64583333334</v>
       </c>
     </row>
     <row r="10">
@@ -1660,126 +1660,513 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="3" t="n">
+        <v>45908.8125</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="3" t="n">
+        <v>45908.83333333334</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>New England II</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Huntsville City</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X12" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK12" s="3" t="n">
+        <v>45908.83333333334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L10" t="n">
+      <c r="L13" t="n">
         <v>1.74</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M13" t="n">
         <v>3.25</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N13" t="n">
         <v>4.5</v>
       </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
         <v>2.38</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z13" t="n">
         <v>1.47</v>
       </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" s="3" t="n">
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3" t="n">
         <v>45908.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK13"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45908.8125</v>
+        <v>45908.79166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45908.83333333334</v>
+        <v>45908.8125</v>
       </c>
     </row>
     <row r="12">
@@ -2047,126 +2047,255 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3" t="n">
+        <v>45908.83333333334</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" t="n">
         <v>1.74</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M14" t="n">
         <v>3.25</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N14" t="n">
         <v>4.5</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
         <v>2.38</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="Z14" t="n">
         <v>1.47</v>
       </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="3" t="n">
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
         <v>45908.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="M13" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="M12" t="n">
         <v>3.2</v>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
         <v>4.5</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
         <v>2.38</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="M9" t="n">
-        <v>3.8</v>
+        <v>3.38</v>
       </c>
       <c r="N9" t="n">
         <v>4.6</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="N11" t="n">
-        <v>4.46</v>
+        <v>3.67</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y11" t="n">
         <v>2.5</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="M12" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="N12" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>2.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M12" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>3.68</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>3.68</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M13" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M12" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>3.68</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>3.68</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M13" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="N13" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M12" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="N12" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z12" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="N13" t="n">
-        <v>2.55</v>
+        <v>3.68</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK14"/>
+  <dimension ref="A1:AK18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.79</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45908.64583333334</v>
+        <v>45908.625</v>
       </c>
     </row>
     <row r="10">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.81</v>
+        <v>2.18</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45908.79166666666</v>
+        <v>45908.625</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.98</v>
+        <v>2.34</v>
       </c>
       <c r="M11" t="n">
-        <v>2.92</v>
+        <v>2.65</v>
       </c>
       <c r="N11" t="n">
-        <v>3.67</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.5</v>
+        <v>2.87</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45908.8125</v>
+        <v>45908.625</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.34</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="N12" t="n">
-        <v>2.55</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.37</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,19 +2026,19 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45908.83333333334</v>
+        <v>45908.64583333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2121,16 +2121,16 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45908.83333333334</v>
+        <v>45908.66666666666</v>
       </c>
     </row>
     <row r="14">
@@ -2176,126 +2176,642 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ferro Carril Oeste</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="M14" t="n">
+        <v>3</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <v>45908.79166666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
+        <v>45908.8125</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="3" t="n">
+        <v>45908.83333333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>New England II</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Huntsville City</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>45908.83333333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>21:30</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L14" t="n">
+      <c r="L18" t="n">
         <v>1.8</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M18" t="n">
         <v>3.3</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N18" t="n">
         <v>4.5</v>
       </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.52</v>
       </c>
-      <c r="X14" t="n">
+      <c r="X18" t="n">
         <v>2.35</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Y18" t="n">
         <v>2.37</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="Z18" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
         <v>45908.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.18</v>
+        <v>2.34</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.57</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.4</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z9" t="n">
         <v>1.57</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.4</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="M10" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>3.35</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,65 +2471,65 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M16" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>3.68</v>
       </c>
       <c r="O17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
         <v>2.87</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.35</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
         <v>2.6</v>
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="N14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="X14" t="n">
         <v>2.1</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,65 +2471,65 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>3.68</v>
       </c>
       <c r="O16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M17" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.35</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,65 +2471,65 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M16" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>3.68</v>
       </c>
       <c r="O17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK18"/>
+  <dimension ref="A1:AK12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45908.45833333334</v>
+        <v>45908.52083333334</v>
       </c>
     </row>
     <row r="3">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45908.45833333334</v>
+        <v>45908.52083333334</v>
       </c>
     </row>
     <row r="4">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45908.45833333334</v>
+        <v>45908.52083333334</v>
       </c>
     </row>
     <row r="5">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1089,16 +1089,16 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45908.52083333334</v>
+        <v>45908.625</v>
       </c>
     </row>
     <row r="6">
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45908.52083333334</v>
+        <v>45908.625</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45908.52083333334</v>
+        <v>45908.625</v>
       </c>
     </row>
     <row r="8">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,16 +1476,16 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45908.5625</v>
+        <v>45908.66666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45908.625</v>
+        <v>45908.79166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>2.92</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>3.67</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45908.625</v>
+        <v>45908.8125</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,49 +1830,49 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
         <v>2.35</v>
       </c>
-      <c r="M11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.87</v>
-      </c>
       <c r="Z11" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45908.625</v>
+        <v>45908.83333333334</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1962,10 +1962,10 @@
         <v>1.79</v>
       </c>
       <c r="M12" t="n">
-        <v>3.38</v>
+        <v>3.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,16 +1992,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.9</v>
+        <v>2.37</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.9</v>
+        <v>1.48</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2038,780 +2038,6 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45908.64583333334</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>45908</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Almirante Brown</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>San Telmo</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="3" t="n">
-        <v>45908.66666666666</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>45908</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Quilmes</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Ferro Carril Oeste</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="N14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="3" t="n">
-        <v>45908.79166666666</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>45908</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Novorizontino</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Atlético GO</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="M15" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="N15" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="3" t="n">
-        <v>45908.8125</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
-        <v>45908</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>New England II</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Huntsville City</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>suspended</t>
-        </is>
-      </c>
-      <c r="L16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="M16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X16" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AK16" s="3" t="n">
-        <v>45908.83333333334</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>45908</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Cuiabá</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>CRB</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="3" t="n">
-        <v>45908.83333333334</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>45908</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="N18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
         <v>45908.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK12"/>
+  <dimension ref="A1:AK18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,12 +628,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -748,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
-        <v>45908.52083333334</v>
+        <v>45908.45833333334</v>
       </c>
     </row>
     <row r="3">
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45908.52083333334</v>
+        <v>45908.45833333334</v>
       </c>
     </row>
     <row r="4">
@@ -886,12 +886,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45908.52083333334</v>
+        <v>45908.45833333334</v>
       </c>
     </row>
     <row r="5">
@@ -1015,27 +1015,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1089,16 +1089,16 @@
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45908.625</v>
+        <v>45908.52083333334</v>
       </c>
     </row>
     <row r="6">
@@ -1144,27 +1144,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45908.625</v>
+        <v>45908.52083333334</v>
       </c>
     </row>
     <row r="7">
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45908.625</v>
+        <v>45908.52083333334</v>
       </c>
     </row>
     <row r="8">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1476,16 +1476,16 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45908.66666666666</v>
+        <v>45908.5625</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="M9" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="N9" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45908.79166666666</v>
+        <v>45908.625</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3.67</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,17 +1734,17 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.55</v>
       </c>
-      <c r="X10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45908.8125</v>
+        <v>45908.625</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.93</v>
+        <v>2.35</v>
       </c>
       <c r="M11" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="N11" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.35</v>
+        <v>2.87</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45908.83333333334</v>
+        <v>45908.625</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1962,82 +1962,856 @@
         <v>1.79</v>
       </c>
       <c r="M12" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="3" t="n">
+        <v>45908.64583333334</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Almirante Brown</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>San Telmo</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3" t="n">
+        <v>45908.66666666666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Quilmes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ferro Carril Oeste</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="N14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3" t="n">
+        <v>45908.79166666666</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Atlético GO</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3" t="n">
+        <v>45908.8125</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>New England II</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Huntsville City</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK16" s="3" t="n">
+        <v>45908.83333333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M17" t="n">
         <v>3.04</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N17" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="3" t="n">
+        <v>45908.83333333334</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N18" t="n">
         <v>4.3</v>
       </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
         <v>1.52</v>
       </c>
-      <c r="X12" t="n">
+      <c r="X18" t="n">
         <v>2.35</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Y18" t="n">
         <v>2.37</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="Z18" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="3" t="n">
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
         <v>45908.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK18"/>
+  <dimension ref="A1:AK20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>3.41</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="M11" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>3.03</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>3.77</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,10 +2250,10 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="M15" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="N15" t="n">
-        <v>3.67</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,16 +2379,16 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="X15" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45908.8125</v>
+        <v>45908.79166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2471,65 +2471,65 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="N16" t="n">
-        <v>2.55</v>
+        <v>3.67</v>
       </c>
       <c r="O16" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="X16" t="n">
-        <v>4.9</v>
+        <v>2.25</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.37</v>
+        <v>1.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,19 +2542,19 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45908.83333333334</v>
+        <v>45908.8125</v>
       </c>
     </row>
     <row r="17">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M17" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z17" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,16 +2671,16 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,85 +2733,343 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
         <v>3.04</v>
       </c>
       <c r="N18" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="3" t="n">
+        <v>45908.83333333334</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N19" t="n">
         <v>4.3</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
         <v>1.52</v>
       </c>
-      <c r="X18" t="n">
+      <c r="X19" t="n">
         <v>2.35</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y19" t="n">
         <v>2.37</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z19" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="3" t="n">
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="3" t="n">
+        <v>45908.89583333334</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cavalier</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3" t="n">
         <v>45908.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>3.41</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
-        <v>3.41</v>
+        <v>2.55</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="M9" t="n">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="N9" t="n">
-        <v>3.41</v>
+        <v>2.55</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,16 +1734,16 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="N11" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
         <v>2.87</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK20"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="M9" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="N9" t="n">
-        <v>2.55</v>
+        <v>3.03</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,16 +1605,16 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.3</v>
+        <v>2.87</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
         <v>2.87</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.41</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.87</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="N19" t="n">
-        <v>4.3</v>
+        <v>6.25</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2895,16 +2895,16 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.37</v>
+        <v>3.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45908.89583333334</v>
+        <v>45908.83333333334</v>
       </c>
     </row>
     <row r="20">
@@ -3070,6 +3070,135 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
+        <v>45908.89583333334</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="3" t="n">
         <v>45908.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK21"/>
+  <dimension ref="A1:AK22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1611,7 +1611,7 @@
         <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Z9" t="n">
         <v>1.4</v>
@@ -1740,7 +1740,7 @@
         <v>2.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="Z10" t="n">
         <v>1.4</v>
@@ -2127,10 +2127,10 @@
         <v>2.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,16 +2250,16 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.95</v>
+        <v>2.36</v>
       </c>
       <c r="M15" t="n">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X15" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,16 +2508,16 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45908.8125</v>
+        <v>45908.79166666666</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,65 +2600,65 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>2.92</v>
       </c>
       <c r="N17" t="n">
-        <v>2.55</v>
+        <v>3.67</v>
       </c>
       <c r="O17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="X17" t="n">
-        <v>4.9</v>
+        <v>2.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.53</v>
+        <v>2.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.37</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,19 +2671,19 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45908.83333333334</v>
+        <v>45908.8125</v>
       </c>
     </row>
     <row r="18">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,65 +2729,65 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="M19" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>6.25</v>
+        <v>3.68</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2895,16 +2895,16 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,16 +3024,16 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45908.89583333334</v>
+        <v>45908.83333333334</v>
       </c>
     </row>
     <row r="21">
@@ -3084,121 +3084,250 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Cavalier</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="3" t="n">
+        <v>45908.89583333334</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>Brazil Serie B</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Vila Nova</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Athletic Club</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr">
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L21" t="n">
+      <c r="L22" t="n">
         <v>1.79</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M22" t="n">
         <v>3.04</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N22" t="n">
         <v>4.3</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
         <v>1.52</v>
       </c>
-      <c r="X21" t="n">
+      <c r="X22" t="n">
         <v>2.35</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Y22" t="n">
         <v>2.37</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="Z22" t="n">
         <v>1.48</v>
       </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="3" t="n">
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="3" t="n">
         <v>45908.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>8.06</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="N9" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Y9" t="n">
         <v>2.75</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="M10" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="N10" t="n">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1734,10 +1734,10 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
         <v>2.75</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2250,16 +2250,16 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N15" t="n">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.65</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.67</v>
-      </c>
       <c r="X15" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2729,65 +2729,65 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>3.68</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.68</v>
+        <v>6.25</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2895,16 +2895,16 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,65 +2987,65 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="M20" t="n">
-        <v>3.06</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>6.25</v>
+        <v>2.55</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="X20" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.1</v>
+        <v>1.53</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.36</v>
+        <v>2.37</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="M3" t="n">
-        <v>4.37</v>
+        <v>3.61</v>
       </c>
       <c r="N3" t="n">
-        <v>8.6</v>
+        <v>5.26</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>3.61</v>
+        <v>4.37</v>
       </c>
       <c r="N4" t="n">
-        <v>5.26</v>
+        <v>8.6</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="M9" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="N9" t="n">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1605,10 +1605,10 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
         <v>2.75</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.44</v>
       </c>
-      <c r="M10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>3.41</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,16 +1863,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2379,16 +2379,16 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N16" t="n">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.65</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.67</v>
-      </c>
       <c r="X16" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.68</v>
+        <v>6.25</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2766,16 +2766,16 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,65 +2858,65 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="M19" t="n">
-        <v>3.06</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>6.25</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.1</v>
+        <v>1.53</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.36</v>
+        <v>2.37</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2987,65 +2987,65 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>2.55</v>
+        <v>3.68</v>
       </c>
       <c r="O20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45908.83333333334</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,16 +3153,16 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -672,10 +672,10 @@
         <v>1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>4.09</v>
+        <v>4.37</v>
       </c>
       <c r="N2" t="n">
-        <v>8.06</v>
+        <v>8.6</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -930,10 +930,10 @@
         <v>1.42</v>
       </c>
       <c r="M4" t="n">
-        <v>4.37</v>
+        <v>4.09</v>
       </c>
       <c r="N4" t="n">
-        <v>8.6</v>
+        <v>8.06</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1581,28 +1581,28 @@
         <v>3.03</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W9" t="n">
         <v>1.6</v>
@@ -1617,16 +1617,16 @@
         <v>1.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>3.41</v>
       </c>
       <c r="O10" t="n">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>4.26</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="U10" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.4</v>
       </c>
-      <c r="X10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA10" t="n">
-        <v>4.35</v>
+        <v>4.85</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,77 +1830,77 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>2.81</v>
+        <v>3.2</v>
       </c>
       <c r="N11" t="n">
-        <v>3.41</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>2.56</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="Z11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2097,28 +2097,28 @@
         <v>3.77</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
         <v>1.5</v>
@@ -2133,16 +2133,16 @@
         <v>1.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N14" t="n">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.65</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.67</v>
-      </c>
       <c r="X14" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="M16" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>6.25</v>
+        <v>3.68</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2766,16 +2766,16 @@
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.68</v>
+        <v>6.25</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,16 +3024,16 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.42</v>
       </c>
-      <c r="M2" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="N2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.61</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>5.26</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.42</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>4.09</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>8.06</v>
+        <v>5.8</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.39</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>4.36</v>
+        <v>4.15</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>5.61</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,43 +1572,43 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="N9" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.92</v>
+        <v>4.26</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>3.92</v>
+        <v>3.65</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Y9" t="n">
         <v>2.75</v>
@@ -1617,16 +1617,16 @@
         <v>1.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.45</v>
+        <v>4.85</v>
       </c>
       <c r="AB9" t="n">
         <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.19</v>
+        <v>2.35</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.59</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,43 +1701,43 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="M10" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="N10" t="n">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.26</v>
+        <v>3.92</v>
       </c>
       <c r="R10" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.65</v>
+        <v>3.92</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
         <v>2.75</v>
@@ -1746,16 +1746,16 @@
         <v>1.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.85</v>
+        <v>5.45</v>
       </c>
       <c r="AB10" t="n">
         <v>1.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.35</v>
+        <v>2.19</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1968,34 +1968,34 @@
         <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y12" t="n">
         <v>1.9</v>
@@ -2004,16 +2004,16 @@
         <v>1.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N16" t="n">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
         <v>1.65</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.67</v>
-      </c>
       <c r="X16" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Talleres Remedios</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2858,65 +2858,65 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.34</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.06</v>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>6.25</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>1.55</v>
       </c>
       <c r="X19" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.53</v>
+        <v>3.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.37</v>
+        <v>1.36</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="M20" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>6.25</v>
+        <v>3.68</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,16 +3024,16 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>3.1</v>
+        <v>2.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,16 +3153,16 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK22"/>
+  <dimension ref="A1:AK21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.47</v>
-      </c>
-      <c r="M2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.42</v>
       </c>
       <c r="S2" t="n">
         <v>2.65</v>
       </c>
       <c r="T2" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="X2" t="n">
-        <v>2.93</v>
+        <v>2.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AB2" t="n">
         <v>1.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.86</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="O3" t="n">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.9</v>
+        <v>7.7</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
         <v>2.65</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AB3" t="n">
         <v>1.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.2</v>
+        <v>2.86</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="N8" t="n">
-        <v>4.15</v>
+        <v>3.41</v>
       </c>
       <c r="O8" t="n">
-        <v>2.44</v>
+        <v>2.93</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.61</v>
+        <v>4.53</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T8" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="U8" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="V8" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.71</v>
+        <v>4.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.16</v>
+        <v>2.35</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.96</v>
+        <v>1.62</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45908.5625</v>
+        <v>45908.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>3.41</v>
+        <v>4.15</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.26</v>
+        <v>5.61</v>
       </c>
       <c r="R9" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T9" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="W9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Z9" t="n">
         <v>1.57</v>
       </c>
-      <c r="X9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AA9" t="n">
-        <v>4.85</v>
+        <v>4.71</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>1.63</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.96</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45908.625</v>
+        <v>45908.5625</v>
       </c>
     </row>
     <row r="10">
@@ -1713,19 +1713,19 @@
         <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="R10" t="n">
         <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.92</v>
+        <v>3.7</v>
       </c>
       <c r="U10" t="n">
         <v>1.25</v>
@@ -1746,16 +1746,16 @@
         <v>1.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
       <c r="AB10" t="n">
         <v>1.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
         <v>2.39</v>
@@ -2118,7 +2118,7 @@
         <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
         <v>1.5</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N14" t="n">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
         <v>1.65</v>
       </c>
-      <c r="S14" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.67</v>
-      </c>
       <c r="X14" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,16 +2508,16 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>3.68</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talleres Remedios</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="M19" t="n">
-        <v>3.06</v>
+        <v>3.6</v>
       </c>
       <c r="N19" t="n">
-        <v>6.25</v>
+        <v>2.55</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.55</v>
+        <v>1.16</v>
       </c>
       <c r="X19" t="n">
-        <v>2.3</v>
+        <v>4.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>3.1</v>
+        <v>1.53</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.36</v>
+        <v>2.37</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2950,27 +2950,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45908.83333333334</v>
+        <v>45908.89583333334</v>
       </c>
     </row>
     <row r="21">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,16 +3153,16 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3199,135 +3199,6 @@
         <v>0</v>
       </c>
       <c r="AK21" s="3" t="n">
-        <v>45908.89583333334</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>45908</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Vila Nova</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="3" t="n">
         <v>45908.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,43 +669,43 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U2" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="X2" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="Y2" t="n">
         <v>2.3</v>
@@ -714,32 +714,32 @@
         <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="AB2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
         <v>1.21</v>
       </c>
-      <c r="AC2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH2" t="n">
-        <v>2.2</v>
+        <v>2.99</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,43 +927,43 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.699999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="T4" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="Y4" t="n">
         <v>2.3</v>
@@ -972,16 +972,16 @@
         <v>1.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.99</v>
+        <v>2.2</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S10" t="n">
         <v>2.44</v>
       </c>
-      <c r="M10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.38</v>
-      </c>
       <c r="T10" t="n">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.35</v>
+        <v>4.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
         <v>1.4</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>3.03</v>
       </c>
       <c r="O11" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="R11" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.4</v>
       </c>
-      <c r="X11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA11" t="n">
-        <v>4.35</v>
+        <v>5.35</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="n">
         <v>1.4</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N15" t="n">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.65</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="T15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.67</v>
-      </c>
       <c r="X15" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>3.68</v>
+        <v>2.55</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M19" t="n">
-        <v>3.6</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>3.68</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3024,16 +3024,16 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3153,16 +3153,16 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,43 +669,43 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="P2" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.699999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S2" t="n">
-        <v>2.58</v>
+        <v>2.65</v>
       </c>
       <c r="T2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="X2" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="Y2" t="n">
         <v>2.3</v>
@@ -714,16 +714,16 @@
         <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.99</v>
+        <v>2.2</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="P3" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="T3" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V3" t="n">
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.36</v>
+        <v>2.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.86</v>
+        <v>2.99</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.26</v>
+        <v>1.94</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.9</v>
+        <v>7.7</v>
       </c>
       <c r="R4" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S4" t="n">
         <v>2.65</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U4" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="X4" t="n">
-        <v>2.75</v>
+        <v>2.93</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AB4" t="n">
         <v>1.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.2</v>
+        <v>2.86</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="M15" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X15" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2613,28 +2613,28 @@
         <v>3.67</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W17" t="n">
         <v>1.55</v>
@@ -2649,16 +2649,16 @@
         <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2871,34 +2871,34 @@
         <v>3.68</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y19" t="n">
         <v>2.35</v>
@@ -2907,16 +2907,16 @@
         <v>1.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -3000,28 +3000,28 @@
         <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="W20" t="n">
         <v>1.52</v>
@@ -3036,16 +3036,16 @@
         <v>1.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.87</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="O2" t="n">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.9</v>
+        <v>8.69</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U2" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X2" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.2</v>
+        <v>2.94</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M3" t="n">
         <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="P3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.699999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="T3" t="n">
-        <v>3.15</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X3" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.55</v>
+        <v>2.14</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.99</v>
+        <v>2.16</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="N4" t="n">
-        <v>6.9</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1.94</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.7</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="R4" t="n">
         <v>1.42</v>
@@ -951,37 +951,37 @@
         <v>2.65</v>
       </c>
       <c r="T4" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X4" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.6</v>
+        <v>3.52</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AH4" t="n">
         <v>2.86</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,77 +1443,77 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.12</v>
+        <v>1.88</v>
       </c>
       <c r="M8" t="n">
-        <v>2.81</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.41</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.93</v>
+        <v>2.64</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.53</v>
+        <v>4.9</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T8" t="n">
-        <v>3.56</v>
+        <v>3.48</v>
       </c>
       <c r="U8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
         <v>1.23</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AH8" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45908.54166666666</v>
+        <v>45908.5625</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,62 +1572,62 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="M9" t="n">
         <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>2.44</v>
+        <v>2.95</v>
       </c>
       <c r="P9" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.61</v>
+        <v>4.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.25</v>
       </c>
-      <c r="Y9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z9" t="n">
+      <c r="AD9" t="n">
         <v>1.57</v>
       </c>
-      <c r="AA9" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AE9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45908.5625</v>
+        <v>45908.625</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>2.79</v>
       </c>
       <c r="N10" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="O10" t="n">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.49</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>3.34</v>
+        <v>3.84</v>
       </c>
       <c r="U10" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="W10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.4</v>
       </c>
-      <c r="X10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA10" t="n">
-        <v>4.35</v>
+        <v>5.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="M11" t="n">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="N11" t="n">
-        <v>3.03</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.78</v>
+        <v>3.44</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="T11" t="n">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="X11" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.35</v>
+        <v>4.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.44</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="M12" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>4.62</v>
       </c>
       <c r="O12" t="n">
-        <v>2.52</v>
+        <v>2.35</v>
       </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>5.48</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S12" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W12" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X12" t="n">
         <v>2.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC12" t="n">
         <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="M13" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.77</v>
+        <v>3.95</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>5.03</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="S13" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="U13" t="n">
         <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
         <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.03</v>
+        <v>5</v>
       </c>
       <c r="AB13" t="n">
         <v>1.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
         <v>1.7</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="M16" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="O16" t="n">
-        <v>2.55</v>
+        <v>3.27</v>
       </c>
       <c r="P16" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3</v>
+        <v>2.14</v>
       </c>
       <c r="T16" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W16" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="X16" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2613,52 +2613,52 @@
         <v>3.67</v>
       </c>
       <c r="O17" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="S17" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V17" t="n">
         <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X17" t="n">
         <v>2.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AA17" t="n">
         <v>5.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
         <v>1.62</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>2.87</v>
       </c>
       <c r="N18" t="n">
-        <v>2.55</v>
+        <v>3.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="X18" t="n">
-        <v>4.9</v>
+        <v>2.64</v>
       </c>
       <c r="Y18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z18" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z18" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AA18" t="n">
-        <v>2.28</v>
+        <v>4.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.42</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.5</v>
+        <v>1.73</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.47</v>
+        <v>1.7</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="M19" t="n">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>3.68</v>
+        <v>2.48</v>
       </c>
       <c r="O19" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>1.87</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>3.34</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>2.63</v>
+        <v>4.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA19" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AC19" t="n">
-        <v>2.04</v>
+        <v>1.42</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.71</v>
+        <v>2.69</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>2.98</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="O20" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.7</v>
+        <v>4.89</v>
       </c>
       <c r="R20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Z20" t="n">
         <v>1.44</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AA20" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>2.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
         <v>1.75</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N2" t="n">
-        <v>6.5</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="P2" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.69</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="R2" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="T2" t="n">
-        <v>3.22</v>
+        <v>3.01</v>
       </c>
       <c r="U2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.3</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.41</v>
-      </c>
       <c r="X2" t="n">
-        <v>2.79</v>
+        <v>2.98</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.22</v>
+        <v>2.02</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.92</v>
+        <v>3.52</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.94</v>
+        <v>2.86</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>8.109999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.130000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S4" t="n">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="T4" t="n">
-        <v>3.01</v>
+        <v>3.22</v>
       </c>
       <c r="U4" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="X4" t="n">
-        <v>2.98</v>
+        <v>2.79</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.52</v>
+        <v>3.92</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>5.26</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -669,28 +669,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>8.109999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="P2" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.130000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T2" t="n">
         <v>3.01</v>
@@ -702,28 +702,28 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X2" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.78</v>
+        <v>1.64</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
         <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
-        <v>2.26</v>
+        <v>1.95</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.75</v>
+        <v>8.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="T3" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.1</v>
+        <v>3.98</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.14</v>
+        <v>2.57</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.16</v>
+        <v>2.91</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.69</v>
+        <v>6.39</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.56</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.92</v>
+        <v>4.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.94</v>
+        <v>2.14</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1443,16 +1443,16 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="O8" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="P8" t="n">
         <v>1.95</v>
@@ -1464,7 +1464,7 @@
         <v>1.53</v>
       </c>
       <c r="S8" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
         <v>3.48</v>
@@ -1476,25 +1476,25 @@
         <v>1.05</v>
       </c>
       <c r="W8" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="Y8" t="n">
         <v>2.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AB8" t="n">
         <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AD8" t="n">
         <v>1.63</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="O9" t="n">
         <v>2.95</v>
@@ -1587,13 +1587,13 @@
         <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="T9" t="n">
         <v>3.6</v>
@@ -1602,22 +1602,22 @@
         <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X9" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="Z9" t="n">
         <v>1.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AB9" t="n">
         <v>1.14</v>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.75</v>
+        <v>2.03</v>
       </c>
       <c r="M10" t="n">
-        <v>2.79</v>
+        <v>3.11</v>
       </c>
       <c r="N10" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X10" t="n">
         <v>2.69</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Y10" t="n">
-        <v>2.63</v>
+        <v>2.02</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="M11" t="n">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>3.03</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.44</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="W11" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1959,34 +1959,34 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="N12" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.48</v>
+        <v>4.75</v>
       </c>
       <c r="R12" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="T12" t="n">
         <v>3.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
         <v>1.02</v>
@@ -1998,22 +1998,22 @@
         <v>2.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.34</v>
+        <v>1.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC12" t="n">
         <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2088,49 +2088,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.9</v>
       </c>
-      <c r="N13" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.76</v>
-      </c>
       <c r="P13" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.03</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
         <v>2.45</v>
       </c>
       <c r="T13" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="U13" t="n">
         <v>1.29</v>
       </c>
       <c r="V13" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
         <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AA13" t="n">
         <v>5</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.78</v>
+        <v>2.36</v>
       </c>
       <c r="M15" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>5.26</v>
+        <v>2.87</v>
       </c>
       <c r="O15" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>4.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X15" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="Z15" t="n">
         <v>1.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N16" t="n">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.27</v>
+        <v>2.58</v>
       </c>
       <c r="P16" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.15</v>
+        <v>6.57</v>
       </c>
       <c r="R16" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="S16" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="T16" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AB16" t="n">
         <v>1.08</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2613,46 +2613,46 @@
         <v>3.67</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S17" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="T17" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V17" t="n">
         <v>1.12</v>
       </c>
       <c r="W17" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="X17" t="n">
         <v>2.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
         <v>5.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AC17" t="n">
         <v>2.2</v>
@@ -2736,16 +2736,16 @@
         <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>2.87</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="O18" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="P18" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
         <v>4.2</v>
@@ -2760,7 +2760,7 @@
         <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
         <v>1.1</v>
@@ -2769,13 +2769,13 @@
         <v>1.44</v>
       </c>
       <c r="X18" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AA18" t="n">
         <v>4.6</v>
@@ -2784,10 +2784,10 @@
         <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
         <v>2.48</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="M9" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="N9" t="n">
-        <v>3.41</v>
+        <v>3.27</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="X9" t="n">
-        <v>2.15</v>
+        <v>2.69</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>3.11</v>
+        <v>2.81</v>
       </c>
       <c r="N10" t="n">
-        <v>3.27</v>
+        <v>3.41</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
-        <v>2.69</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.02</v>
+        <v>2.75</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>2.37</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>3.68</v>
+        <v>2.48</v>
       </c>
       <c r="O18" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.2</v>
+        <v>2.95</v>
       </c>
       <c r="R18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.5</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.37</v>
+        <v>1.93</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.48</v>
+        <v>3.68</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>4.3</v>
+        <v>2.63</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.18</v>
+        <v>4.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="P2" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.4</v>
+        <v>8.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="T2" t="n">
-        <v>3.01</v>
+        <v>3.22</v>
       </c>
       <c r="U2" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="X2" t="n">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.44</v>
+        <v>3.98</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.29</v>
+        <v>2.57</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="T3" t="n">
-        <v>3.22</v>
+        <v>3.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="X3" t="n">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.98</v>
+        <v>3.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.57</v>
+        <v>2.29</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.03</v>
+        <v>2.44</v>
       </c>
       <c r="M9" t="n">
-        <v>3.11</v>
+        <v>2.63</v>
       </c>
       <c r="N9" t="n">
-        <v>3.27</v>
+        <v>3.03</v>
       </c>
       <c r="O9" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="P9" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.02</v>
+        <v>2.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="M10" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="N10" t="n">
-        <v>3.41</v>
+        <v>3.27</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="X10" t="n">
-        <v>2.15</v>
+        <v>2.69</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,43 +1830,43 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="N11" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="O11" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.6</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.7</v>
       </c>
       <c r="U11" t="n">
         <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
         <v>2.75</v>
@@ -1875,16 +1875,16 @@
         <v>1.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>6.57</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,43 +669,43 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.6</v>
+        <v>6.39</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X2" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="Y2" t="n">
         <v>2.3</v>
@@ -714,16 +714,16 @@
         <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.98</v>
+        <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.91</v>
+        <v>2.14</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,43 +927,43 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="P4" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.39</v>
+        <v>8.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U4" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="Y4" t="n">
         <v>2.3</v>
@@ -972,16 +972,16 @@
         <v>1.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.5</v>
+        <v>3.98</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.14</v>
+        <v>2.91</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,43 +1572,43 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="N9" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="O9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="T9" t="n">
         <v>3.6</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.7</v>
       </c>
       <c r="U9" t="n">
         <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Y9" t="n">
         <v>2.75</v>
@@ -1617,16 +1617,16 @@
         <v>1.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.03</v>
+        <v>2.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.11</v>
+        <v>2.63</v>
       </c>
       <c r="N10" t="n">
-        <v>3.27</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.02</v>
+        <v>2.75</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="M11" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="N11" t="n">
-        <v>3.41</v>
+        <v>3.27</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>2.69</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.4</v>
+        <v>1.59</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N14" t="n">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>2.58</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.15</v>
+        <v>6.57</v>
       </c>
       <c r="R14" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="T14" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X14" t="n">
         <v>2.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="Z14" t="n">
         <v>1.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.33</v>
+        <v>2.51</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.48</v>
+        <v>1.85</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="M15" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="O15" t="n">
-        <v>2.58</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.57</v>
+        <v>4.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X15" t="n">
         <v>2.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Z15" t="n">
         <v>1.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.51</v>
+        <v>2.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.85</v>
+        <v>1.48</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,62 +669,62 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="O2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2.29</v>
       </c>
-      <c r="P2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z2" t="n">
+      <c r="AD2" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AE2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.14</v>
+        <v>2.86</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>6.9</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="T3" t="n">
-        <v>3.01</v>
+        <v>3.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.29</v>
+        <v>2.57</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,43 +927,43 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="P4" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.6</v>
+        <v>5.95</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.35</v>
+        <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
         <v>2.3</v>
@@ -972,16 +972,16 @@
         <v>1.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.98</v>
+        <v>5.16</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.91</v>
+        <v>2.14</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1452,7 +1452,7 @@
         <v>4.15</v>
       </c>
       <c r="O8" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="P8" t="n">
         <v>1.95</v>
@@ -1485,13 +1485,13 @@
         <v>2.55</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.6</v>
+        <v>4.96</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AC8" t="n">
         <v>2.17</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,43 +1572,43 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="M9" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="N9" t="n">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="O9" t="n">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="T9" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U9" t="n">
         <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
         <v>2.75</v>
@@ -1617,16 +1617,16 @@
         <v>1.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,43 +1701,43 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="O10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T10" t="n">
         <v>3.6</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.7</v>
       </c>
       <c r="U10" t="n">
         <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
         <v>2.75</v>
@@ -1746,7 +1746,7 @@
         <v>1.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AB10" t="n">
         <v>1.13</v>
@@ -1755,7 +1755,7 @@
         <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1971,28 +1971,28 @@
         <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S12" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
         <v>3.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
         <v>2.7</v>
@@ -2004,13 +2004,13 @@
         <v>1.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
         <v>1.67</v>
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AH12" t="n">
         <v>1.95</v>
@@ -2097,28 +2097,28 @@
         <v>3.77</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="R13" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="S13" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="T13" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="U13" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
         <v>1.5</v>
@@ -2133,32 +2133,32 @@
         <v>1.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.67</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.57</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2355,22 +2355,22 @@
         <v>2.87</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
         <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="R15" t="n">
         <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
         <v>1.2</v>
@@ -2379,28 +2379,28 @@
         <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.92</v>
+        <v>3.11</v>
       </c>
       <c r="Z15" t="n">
         <v>1.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.8</v>
+        <v>6.25</v>
       </c>
       <c r="AB15" t="n">
         <v>1.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2613,16 +2613,16 @@
         <v>3.67</v>
       </c>
       <c r="O17" t="n">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="P17" t="n">
         <v>1.91</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="S17" t="n">
         <v>2.25</v>
@@ -2631,10 +2631,10 @@
         <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
         <v>1.55</v>
@@ -2652,13 +2652,13 @@
         <v>5.75</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AC17" t="n">
         <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2871,31 +2871,31 @@
         <v>3.68</v>
       </c>
       <c r="O19" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.2</v>
+        <v>5.03</v>
       </c>
       <c r="R19" t="n">
         <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
         <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="V19" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W19" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="X19" t="n">
         <v>2.63</v>
@@ -2907,16 +2907,16 @@
         <v>1.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.6</v>
+        <v>4.15</v>
       </c>
       <c r="AB19" t="n">
         <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N2" t="n">
-        <v>6.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1.93</v>
       </c>
       <c r="P2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y2" t="n">
         <v>2.19</v>
       </c>
-      <c r="Q2" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X2" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.12</v>
-      </c>
       <c r="Z2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.44</v>
+        <v>3.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,62 +798,62 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.9</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="T3" t="n">
-        <v>3.22</v>
+        <v>3.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="X3" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="Z3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.55</v>
       </c>
-      <c r="AA3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AE3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="O4" t="n">
         <v>2.29</v>
@@ -960,16 +960,16 @@
         <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
         <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AA4" t="n">
         <v>5.16</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="M8" t="n">
         <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="O8" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="T8" t="n">
-        <v>3.48</v>
+        <v>3.66</v>
       </c>
       <c r="U8" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X8" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.55</v>
+        <v>2.89</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.96</v>
+        <v>5.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="M10" t="n">
-        <v>2.81</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>3.41</v>
+        <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
         <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
-        <v>3.11</v>
+        <v>2.81</v>
       </c>
       <c r="N11" t="n">
-        <v>3.27</v>
+        <v>3.41</v>
       </c>
       <c r="O11" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P11" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S11" t="n">
         <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>2.69</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.02</v>
+        <v>2.75</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.59</v>
+        <v>1.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="O12" t="n">
         <v>2.45</v>
@@ -1977,10 +1977,10 @@
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="T12" t="n">
         <v>3.28</v>
@@ -1998,10 +1998,10 @@
         <v>2.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.9</v>
+        <v>2.03</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA12" t="n">
         <v>4.3</v>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,28 +2475,28 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="M16" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T16" t="n">
         <v>4</v>
@@ -2508,28 +2508,28 @@
         <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X16" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="Z16" t="n">
         <v>1.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2613,22 +2613,22 @@
         <v>3.67</v>
       </c>
       <c r="O17" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="R17" t="n">
         <v>1.61</v>
       </c>
       <c r="S17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="U17" t="n">
         <v>1.25</v>
@@ -2637,19 +2637,19 @@
         <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="X17" t="n">
         <v>2.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.75</v>
+        <v>4.9</v>
       </c>
       <c r="AB17" t="n">
         <v>1.13</v>
@@ -2671,7 +2671,7 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
         <v>1.68</v>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
         <v>2.48</v>
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.04</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>3.68</v>
+        <v>5.2</v>
       </c>
       <c r="O19" t="n">
-        <v>2.76</v>
+        <v>2.46</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.03</v>
+        <v>5.76</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U19" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="X19" t="n">
         <v>2.63</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AA19" t="n">
         <v>4.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="O20" t="n">
         <v>2.7</v>
@@ -3006,10 +3006,10 @@
         <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.5</v>
+        <v>4.97</v>
       </c>
       <c r="R20" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
         <v>2.3</v>
@@ -3024,13 +3024,13 @@
         <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X20" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Z20" t="n">
         <v>1.48</v>
@@ -3045,7 +3045,7 @@
         <v>2.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="M2" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.69</v>
+        <v>5.95</v>
       </c>
       <c r="R2" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="X2" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.19</v>
+        <v>2.42</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.92</v>
+        <v>5.16</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.04</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.95</v>
+        <v>2.14</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,77 +927,77 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>8.69</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z4" t="n">
         <v>1.65</v>
       </c>
-      <c r="M4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V4" t="n">
+      <c r="AA4" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
         <v>1.04</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH4" t="n">
-        <v>2.14</v>
+        <v>2.95</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.44</v>
+        <v>2.08</v>
       </c>
       <c r="M9" t="n">
-        <v>2.63</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>3.03</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3.55</v>
+        <v>2.76</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.4</v>
+        <v>1.61</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.25</v>
+        <v>4.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>2.81</v>
       </c>
       <c r="N10" t="n">
-        <v>2.5</v>
+        <v>3.41</v>
       </c>
       <c r="O10" t="n">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="S10" t="n">
         <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.02</v>
+        <v>2.75</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="M11" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="N11" t="n">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="P11" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U11" t="n">
         <v>1.25</v>
@@ -1863,10 +1863,10 @@
         <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Y11" t="n">
         <v>2.75</v>
@@ -1875,16 +1875,16 @@
         <v>1.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AB11" t="n">
         <v>1.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,28 +2217,28 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
         <v>4</v>
@@ -2250,28 +2250,28 @@
         <v>1.14</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X14" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="Z14" t="n">
         <v>1.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="N3" t="n">
-        <v>6.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1.93</v>
       </c>
       <c r="P3" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.130000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="T3" t="n">
-        <v>3.01</v>
+        <v>3.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="X3" t="n">
-        <v>3.04</v>
+        <v>2.79</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.44</v>
+        <v>3.92</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="N4" t="n">
-        <v>8.199999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.93</v>
       </c>
       <c r="P4" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.69</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="T4" t="n">
-        <v>3.22</v>
+        <v>3.01</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="X4" t="n">
-        <v>2.79</v>
+        <v>3.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.92</v>
+        <v>3.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,31 +1701,31 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="M10" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="N10" t="n">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
-        <v>2.95</v>
+        <v>3.55</v>
       </c>
       <c r="P10" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U10" t="n">
         <v>1.25</v>
@@ -1734,10 +1734,10 @@
         <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
         <v>2.75</v>
@@ -1746,16 +1746,16 @@
         <v>1.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AB10" t="n">
         <v>1.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="N11" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="O11" t="n">
-        <v>3.55</v>
+        <v>2.95</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="Q11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T11" t="n">
         <v>3.6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.7</v>
       </c>
       <c r="U11" t="n">
         <v>1.25</v>
@@ -1863,10 +1863,10 @@
         <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
         <v>2.75</v>
@@ -1875,16 +1875,16 @@
         <v>1.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AB11" t="n">
         <v>1.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2625,7 +2625,7 @@
         <v>1.61</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="T17" t="n">
         <v>3.55</v>
@@ -2655,7 +2655,7 @@
         <v>1.13</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD17" t="n">
         <v>1.54</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.48</v>
+        <v>3.76</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.95</v>
+        <v>5.81</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2.1</v>
       </c>
-      <c r="U18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AD18" t="n">
-        <v>2.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.2</v>
+        <v>2.48</v>
       </c>
       <c r="O19" t="n">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.76</v>
+        <v>2.95</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>3.28</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>2.63</v>
+        <v>4.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.53</v>
+        <v>2.37</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.15</v>
+        <v>2.18</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.16</v>
+        <v>1.52</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="N20" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O20" t="n">
         <v>2.7</v>
@@ -3006,16 +3006,16 @@
         <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.97</v>
+        <v>4.89</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
         <v>2.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
         <v>1.25</v>
@@ -3027,25 +3027,25 @@
         <v>1.53</v>
       </c>
       <c r="X20" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AA20" t="n">
         <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
         <v>1.7</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>5.2</v>
+        <v>6.9</v>
       </c>
       <c r="O2" t="n">
-        <v>2.29</v>
+        <v>1.93</v>
       </c>
       <c r="P2" t="n">
-        <v>2.01</v>
+        <v>2.37</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.95</v>
+        <v>8.26</v>
       </c>
       <c r="R2" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="U2" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="X2" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.16</v>
+        <v>3.44</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.14</v>
+        <v>2.86</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,28 +798,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>8.199999999999999</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.69</v>
+        <v>6.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="T3" t="n">
         <v>3.22</v>
@@ -831,28 +831,28 @@
         <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X3" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,77 +927,77 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
       <c r="M4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N4" t="n">
         <v>4.3</v>
       </c>
-      <c r="N4" t="n">
-        <v>6.1</v>
-      </c>
       <c r="O4" t="n">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="P4" t="n">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.130000000000001</v>
+        <v>5.95</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>3.01</v>
+        <v>3.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
         <v>1.29</v>
       </c>
-      <c r="X4" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AH4" t="n">
-        <v>2.86</v>
+        <v>2.14</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
         <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="O8" t="n">
         <v>2.9</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="R8" t="n">
         <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="T8" t="n">
-        <v>3.66</v>
+        <v>3.88</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.89</v>
+        <v>2.48</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AA8" t="n">
         <v>5.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,37 +1572,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
         <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="P9" t="n">
         <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V9" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
         <v>1.36</v>
@@ -1614,19 +1614,19 @@
         <v>2.02</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AB9" t="n">
         <v>1.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
         <v>1.73</v>
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="M10" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>2.7</v>
       </c>
       <c r="O10" t="n">
         <v>3.55</v>
@@ -1716,7 +1716,7 @@
         <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R10" t="n">
         <v>1.53</v>
@@ -1725,7 +1725,7 @@
         <v>2.38</v>
       </c>
       <c r="T10" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
         <v>1.25</v>
@@ -1734,19 +1734,19 @@
         <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="X10" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.25</v>
+        <v>5.3</v>
       </c>
       <c r="AB10" t="n">
         <v>1.13</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="M11" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>3.41</v>
+        <v>3.65</v>
       </c>
       <c r="O11" t="n">
         <v>2.95</v>
@@ -1845,13 +1845,13 @@
         <v>1.89</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="R11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.23</v>
       </c>
       <c r="T11" t="n">
         <v>3.6</v>
@@ -1863,13 +1863,13 @@
         <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="Z11" t="n">
         <v>1.4</v>
@@ -1878,7 +1878,7 @@
         <v>5.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC11" t="n">
         <v>2.2</v>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2088,28 +2088,28 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>3.77</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P13" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q13" t="n">
         <v>5.05</v>
       </c>
       <c r="R13" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
         <v>3.8</v>
@@ -2118,22 +2118,22 @@
         <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="X13" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.55</v>
+        <v>2.74</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="AB13" t="n">
         <v>1.11</v>
@@ -2142,7 +2142,7 @@
         <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
         <v>1.67</v>
@@ -2226,13 +2226,13 @@
         <v>2.87</v>
       </c>
       <c r="O14" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
         <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
         <v>1.62</v>
@@ -2244,19 +2244,19 @@
         <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
         <v>1.14</v>
       </c>
       <c r="W14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="Z14" t="n">
         <v>1.36</v>
@@ -2475,28 +2475,28 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="M16" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>4.46</v>
       </c>
       <c r="O16" t="n">
         <v>2.75</v>
       </c>
       <c r="P16" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
         <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T16" t="n">
         <v>4</v>
@@ -2508,22 +2508,22 @@
         <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
         <v>5.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AC16" t="n">
         <v>2.5</v>
@@ -2542,7 +2542,7 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AH16" t="n">
         <v>1.77</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>3.76</v>
+        <v>2.48</v>
       </c>
       <c r="O18" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.81</v>
+        <v>2.95</v>
       </c>
       <c r="R18" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>2.64</v>
+        <v>4.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.51</v>
+        <v>2.37</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.15</v>
+        <v>2.18</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="AC18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.34</v>
+        <v>1.72</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.48</v>
+        <v>3.76</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.95</v>
+        <v>5.81</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.1</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="X19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AD19" t="n">
-        <v>2.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.5</v>
+        <v>1.91</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,77 +1572,77 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.04</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="N9" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="O9" t="n">
-        <v>2.63</v>
+        <v>3.55</v>
       </c>
       <c r="P9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W9" t="n">
+      <c r="AD9" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.36</v>
       </c>
-      <c r="X9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH9" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.6</v>
+        <v>2.03</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>3.11</v>
       </c>
       <c r="N10" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X10" t="n">
         <v>2.7</v>
       </c>
-      <c r="O10" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Y10" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
         <v>4.33</v>
@@ -1971,7 +1971,7 @@
         <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
         <v>5</v>
@@ -1983,37 +1983,37 @@
         <v>2.63</v>
       </c>
       <c r="T12" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
         <v>1.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W12" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
         <v>2.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.03</v>
+        <v>2.31</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AA12" t="n">
         <v>4.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2616,65 +2616,65 @@
         <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="Q17" t="n">
         <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S17" t="n">
         <v>2.25</v>
       </c>
       <c r="T17" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="W17" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="X17" t="n">
         <v>2.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="Z17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
         <v>1.4</v>
       </c>
-      <c r="AA17" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.34</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>2.48</v>
+        <v>3.68</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.95</v>
+        <v>5.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="X18" t="n">
-        <v>4.3</v>
+        <v>2.63</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.18</v>
+        <v>4.15</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.42</v>
+        <v>2.11</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.72</v>
+        <v>2.34</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>3.76</v>
+        <v>2.48</v>
       </c>
       <c r="O19" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.81</v>
+        <v>2.95</v>
       </c>
       <c r="R19" t="n">
-        <v>1.48</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
-        <v>2.64</v>
+        <v>4.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.38</v>
+        <v>1.53</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.51</v>
+        <v>2.37</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.15</v>
+        <v>2.18</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.2</v>
+        <v>1.52</v>
       </c>
       <c r="AC19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,77 +669,77 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.37</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.26</v>
+        <v>5.95</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
         <v>1.29</v>
       </c>
-      <c r="X2" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AH2" t="n">
-        <v>2.86</v>
+        <v>2.13</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
         <v>5.8</v>
       </c>
       <c r="O3" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="P3" t="n">
         <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.9</v>
+        <v>8.84</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
         <v>2.53</v>
       </c>
       <c r="T3" t="n">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="U3" t="n">
         <v>1.3</v>
@@ -843,16 +843,16 @@
         <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="O4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC4" t="n">
         <v>2.29</v>
       </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.14</v>
+        <v>2.86</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1452,28 +1452,28 @@
         <v>4.15</v>
       </c>
       <c r="O8" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="P8" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="R8" t="n">
         <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.88</v>
+        <v>3.66</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V8" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
         <v>1.55</v>
@@ -1488,16 +1488,16 @@
         <v>1.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.92</v>
+        <v>5.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.32</v>
+        <v>2.21</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.6</v>
+        <v>2.44</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="N9" t="n">
-        <v>2.7</v>
+        <v>3.03</v>
       </c>
       <c r="O9" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="P9" t="n">
         <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R9" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T9" t="n">
         <v>3.8</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W9" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.3</v>
+        <v>5.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         <v>1.36</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1830,49 +1830,49 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="N11" t="n">
-        <v>3.65</v>
+        <v>3.41</v>
       </c>
       <c r="O11" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P11" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
         <v>1.53</v>
       </c>
       <c r="S11" t="n">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W11" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.59</v>
+        <v>2.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AA11" t="n">
         <v>5.5</v>
@@ -1881,10 +1881,10 @@
         <v>1.14</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
-        <v>3.25</v>
+        <v>3.38</v>
       </c>
       <c r="N12" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>2.45</v>
@@ -1998,10 +1998,10 @@
         <v>2.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.31</v>
+        <v>1.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="n">
         <v>4.3</v>
@@ -2088,16 +2088,16 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="N13" t="n">
-        <v>4</v>
+        <v>3.77</v>
       </c>
       <c r="O13" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
         <v>1.78</v>
@@ -2112,28 +2112,28 @@
         <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="V13" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.74</v>
+        <v>2.85</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="AB13" t="n">
         <v>1.11</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,22 +2217,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="N14" t="n">
-        <v>2.87</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P14" t="n">
         <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="R14" t="n">
         <v>1.62</v>
@@ -2241,37 +2241,37 @@
         <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="V14" t="n">
         <v>1.14</v>
       </c>
       <c r="W14" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X14" t="n">
         <v>2.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
         <v>2.48</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,43 +669,43 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>2.29</v>
+        <v>1.95</v>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.95</v>
+        <v>8.84</v>
       </c>
       <c r="R2" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="T2" t="n">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="U2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="X2" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="Y2" t="n">
         <v>2.3</v>
@@ -714,16 +714,16 @@
         <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.5</v>
+        <v>3.98</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.13</v>
+        <v>2.9</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.84</v>
+        <v>7.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="S3" t="n">
-        <v>2.53</v>
+        <v>2.69</v>
       </c>
       <c r="T3" t="n">
-        <v>3.32</v>
+        <v>2.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="X3" t="n">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.98</v>
+        <v>3.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,77 +927,77 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.5</v>
+        <v>5.95</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="S4" t="n">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="T4" t="n">
-        <v>2.99</v>
+        <v>3.4</v>
       </c>
       <c r="U4" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
         <v>1.29</v>
       </c>
-      <c r="X4" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH4" t="n">
-        <v>2.86</v>
+        <v>2.13</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.44</v>
+        <v>2.03</v>
       </c>
       <c r="M9" t="n">
-        <v>2.63</v>
+        <v>3.11</v>
       </c>
       <c r="N9" t="n">
-        <v>3.03</v>
+        <v>3.27</v>
       </c>
       <c r="O9" t="n">
-        <v>3.56</v>
+        <v>2.76</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="T9" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="X9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y9" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y9" t="n">
-        <v>2.85</v>
-      </c>
       <c r="Z9" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.03</v>
+        <v>2.44</v>
       </c>
       <c r="M10" t="n">
-        <v>3.11</v>
+        <v>2.63</v>
       </c>
       <c r="N10" t="n">
-        <v>3.27</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
-        <v>2.76</v>
+        <v>3.56</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="S10" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC10" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AD10" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,22 +2217,22 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.84</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>2.87</v>
       </c>
       <c r="O14" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.25</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
         <v>1.62</v>
@@ -2241,37 +2241,37 @@
         <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="U14" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="V14" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.04</v>
+        <v>3.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AA14" t="n">
         <v>6</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>1.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>2.38</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>3.68</v>
+        <v>2.48</v>
       </c>
       <c r="O18" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.6</v>
+        <v>2.95</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
-        <v>2.63</v>
+        <v>4.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB18" t="n">
         <v>1.52</v>
       </c>
-      <c r="AA18" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AC18" t="n">
-        <v>2.11</v>
+        <v>1.42</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.66</v>
+        <v>2.69</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.48</v>
+        <v>3.68</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.95</v>
+        <v>5.6</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="X19" t="n">
-        <v>4.3</v>
+        <v>2.63</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.18</v>
+        <v>4.15</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.42</v>
+        <v>2.11</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,43 +669,43 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.95</v>
+        <v>2.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>8.84</v>
+        <v>5.95</v>
       </c>
       <c r="R2" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="S2" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="T2" t="n">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="X2" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="Y2" t="n">
         <v>2.3</v>
@@ -714,16 +714,16 @@
         <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.98</v>
+        <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.9</v>
+        <v>2.13</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="P3" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.5</v>
+        <v>8.84</v>
       </c>
       <c r="R3" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="S3" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="T3" t="n">
-        <v>2.99</v>
+        <v>3.32</v>
       </c>
       <c r="U3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.35</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.29</v>
-      </c>
       <c r="X3" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.44</v>
+        <v>3.98</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="O4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC4" t="n">
         <v>2.29</v>
       </c>
-      <c r="P4" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD4" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.13</v>
+        <v>2.86</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="N9" t="n">
-        <v>3.27</v>
+        <v>3.6</v>
       </c>
       <c r="O9" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="X9" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.44</v>
+        <v>2.03</v>
       </c>
       <c r="M10" t="n">
-        <v>2.63</v>
+        <v>3.11</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>3.27</v>
       </c>
       <c r="O10" t="n">
-        <v>3.56</v>
+        <v>2.76</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="S10" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="T10" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="X10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y10" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y10" t="n">
-        <v>2.85</v>
-      </c>
       <c r="Z10" t="n">
-        <v>1.37</v>
+        <v>1.55</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="M11" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="N11" t="n">
-        <v>3.41</v>
+        <v>2.74</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="S11" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="U11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.4</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.6</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2088,58 +2088,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="M13" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="N13" t="n">
-        <v>3.77</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
         <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.05</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X13" t="n">
         <v>2.25</v>
       </c>
-      <c r="T13" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.4</v>
-      </c>
       <c r="Y13" t="n">
-        <v>2.85</v>
+        <v>2.74</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="AB13" t="n">
         <v>1.11</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="AD13" t="n">
         <v>1.53</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2229,49 +2229,49 @@
         <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="U14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
         <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="X14" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.09</v>
+        <v>3.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2346,58 +2346,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="M15" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>2.79</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.25</v>
+        <v>5.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S15" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T15" t="n">
-        <v>3.98</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
         <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="X15" t="n">
         <v>2.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA15" t="n">
         <v>6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD15" t="n">
         <v>1.5</v>
@@ -2416,7 +2416,7 @@
         <v>1.4</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="O2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2.29</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AD2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.13</v>
+        <v>2.81</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,43 +798,43 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.95</v>
+        <v>2.38</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.84</v>
+        <v>6.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="T3" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="X3" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="Y3" t="n">
         <v>2.3</v>
@@ -843,16 +843,16 @@
         <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.98</v>
+        <v>4.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.9</v>
+        <v>2.14</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="P4" t="n">
-        <v>2.37</v>
+        <v>2.19</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.5</v>
+        <v>10.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="T4" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="X4" t="n">
-        <v>3.04</v>
+        <v>2.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.44</v>
+        <v>3.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.29</v>
+        <v>2.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.56</v>
+        <v>1.39</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1452,28 +1452,28 @@
         <v>4.15</v>
       </c>
       <c r="O8" t="n">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="P8" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.55</v>
+        <v>4.7</v>
       </c>
       <c r="R8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="T8" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
         <v>1.55</v>
@@ -1488,16 +1488,16 @@
         <v>1.45</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.05</v>
+        <v>5.35</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="P9" t="n">
         <v>2.1</v>
       </c>
-      <c r="M9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="N9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="R9" t="n">
-        <v>1.61</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="T9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z9" t="n">
         <v>1.55</v>
       </c>
-      <c r="X9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AA9" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="M10" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.27</v>
+        <v>3.6</v>
       </c>
       <c r="O10" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="S10" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.77</v>
+        <v>1.48</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1971,28 +1971,28 @@
         <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="S12" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="X12" t="n">
         <v>2.7</v>
@@ -2004,16 +2004,16 @@
         <v>1.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="O20" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>6.9</v>
+        <v>5.38</v>
       </c>
       <c r="O2" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="P2" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>2.69</v>
+        <v>2.42</v>
       </c>
       <c r="T2" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X2" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.52</v>
+        <v>4.55</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.21</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.81</v>
+        <v>2.14</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,62 +798,62 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.87</v>
+        <v>1.39</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>4.22</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.1</v>
+        <v>7.7</v>
       </c>
       <c r="R3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.51</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AE3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.14</v>
+        <v>2.81</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="N4" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="P4" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="Q4" t="n">
-        <v>10.2</v>
+        <v>9.1</v>
       </c>
       <c r="R4" t="n">
         <v>1.44</v>
@@ -951,25 +951,25 @@
         <v>2.59</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="X4" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AA4" t="n">
         <v>3.74</v>
@@ -978,10 +978,10 @@
         <v>1.19</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.82</v>
+        <v>2.1</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="M6" t="n">
         <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Z6" t="n">
         <v>1.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>2.93</v>
       </c>
       <c r="N8" t="n">
-        <v>4.15</v>
+        <v>3.77</v>
       </c>
       <c r="O8" t="n">
         <v>2.94</v>
@@ -1458,7 +1458,7 @@
         <v>1.88</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="R8" t="n">
         <v>1.63</v>
@@ -1473,19 +1473,19 @@
         <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="X8" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.48</v>
+        <v>2.83</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AA8" t="n">
         <v>5.35</v>
@@ -1494,10 +1494,10 @@
         <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="M9" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.27</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S9" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="T9" t="n">
         <v>3.2</v>
@@ -1602,31 +1602,31 @@
         <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="X9" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="M10" t="n">
         <v>2.8</v>
       </c>
       <c r="N10" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="S10" t="n">
         <v>2.25</v>
       </c>
       <c r="T10" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X10" t="n">
         <v>2.3</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.59</v>
+        <v>3.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="M11" t="n">
-        <v>2.65</v>
+        <v>2.93</v>
       </c>
       <c r="N11" t="n">
-        <v>2.74</v>
+        <v>3.65</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="P11" t="n">
         <v>1.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="S11" t="n">
         <v>2.25</v>
       </c>
       <c r="T11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X11" t="n">
         <v>2.3</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="M12" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O12" t="n">
         <v>2.45</v>
@@ -1980,13 +1980,13 @@
         <v>1.49</v>
       </c>
       <c r="S12" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="T12" t="n">
         <v>3.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
         <v>1.06</v>
@@ -1998,10 +1998,10 @@
         <v>2.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AA12" t="n">
         <v>4</v>
@@ -2013,7 +2013,7 @@
         <v>2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2091,19 +2091,19 @@
         <v>2.07</v>
       </c>
       <c r="M13" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
         <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
         <v>1.65</v>
@@ -2124,13 +2124,13 @@
         <v>1.62</v>
       </c>
       <c r="X13" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Y13" t="n">
         <v>2.74</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AA13" t="n">
         <v>5.65</v>
@@ -2142,7 +2142,7 @@
         <v>2.37</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH13" t="n">
         <v>1.7</v>
@@ -2238,7 +2238,7 @@
         <v>1.67</v>
       </c>
       <c r="S14" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
         <v>4.45</v>
@@ -2265,10 +2265,10 @@
         <v>6.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
         <v>1.44</v>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2349,13 +2349,13 @@
         <v>2.1</v>
       </c>
       <c r="M15" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="N15" t="n">
         <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="P15" t="n">
         <v>1.8</v>
@@ -2364,16 +2364,16 @@
         <v>5.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="V15" t="n">
         <v>1.14</v>
@@ -2382,25 +2382,25 @@
         <v>1.63</v>
       </c>
       <c r="X15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Y15" t="n">
         <v>3</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
         <v>6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2484,52 +2484,52 @@
         <v>5.4</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2616,25 +2616,25 @@
         <v>2.75</v>
       </c>
       <c r="P17" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="Q17" t="n">
         <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S17" t="n">
         <v>2.25</v>
       </c>
       <c r="T17" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="V17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
         <v>1.55</v>
@@ -2649,16 +2649,16 @@
         <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.75</v>
+        <v>4.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AC17" t="n">
         <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2871,34 +2871,34 @@
         <v>3.68</v>
       </c>
       <c r="O19" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
         <v>2.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
         <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W19" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="Y19" t="n">
         <v>2.35</v>
@@ -2907,16 +2907,16 @@
         <v>1.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.15</v>
+        <v>4.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.05</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.26</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>3.01</v>
       </c>
       <c r="O21" t="n">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="P21" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="S21" t="n">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="T21" t="n">
-        <v>3.6</v>
+        <v>2.84</v>
       </c>
       <c r="U21" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>5</v>
+        <v>3.34</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.17</v>
+        <v>1.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>4.22</v>
       </c>
       <c r="N2" t="n">
-        <v>5.38</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="P2" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>7.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="T2" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.55</v>
+        <v>3.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.27</v>
+        <v>2.41</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.14</v>
+        <v>2.81</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>4.22</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>8.460000000000001</v>
+        <v>5.38</v>
       </c>
       <c r="O3" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="P3" t="n">
-        <v>2.16</v>
+        <v>1.99</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.7</v>
+        <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.16</v>
+        <v>2.56</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.8</v>
+        <v>4.55</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.41</v>
+        <v>2.27</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.81</v>
+        <v>2.14</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,28 +1056,28 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="M5" t="n">
         <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
         <v>2.62</v>
@@ -1086,47 +1086,47 @@
         <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X5" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,28 +1185,28 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="R6" t="n">
         <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="T6" t="n">
         <v>2.62</v>
@@ -1218,28 +1218,28 @@
         <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AB6" t="n">
         <v>1.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="M7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N7" t="n">
         <v>3.2</v>
       </c>
-      <c r="N7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O7" t="n">
-        <v>2.35</v>
+        <v>2.72</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="R7" t="n">
         <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="T7" t="n">
         <v>2.62</v>
@@ -1344,31 +1344,31 @@
         <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.04</v>
+        <v>2.72</v>
       </c>
       <c r="M9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y9" t="n">
         <v>3.1</v>
       </c>
-      <c r="N9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.18</v>
-      </c>
       <c r="Z9" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="M10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X10" t="n">
         <v>2.8</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Y10" t="n">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.75</v>
+        <v>3.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="N14" t="n">
-        <v>2.87</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>2.84</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.1</v>
+        <v>5.12</v>
       </c>
       <c r="R14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="T14" t="n">
-        <v>4.45</v>
+        <v>3.95</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W14" t="n">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.1</v>
       </c>
-      <c r="M15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5.12</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.25</v>
-      </c>
       <c r="T15" t="n">
-        <v>3.95</v>
+        <v>4.45</v>
       </c>
       <c r="U15" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="X15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>3.42</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AA16" t="n">
         <v>3.05</v>
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="M17" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
         <v>2.75</v>
@@ -2631,28 +2631,28 @@
         <v>3.6</v>
       </c>
       <c r="U17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X17" t="n">
         <v>2.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AA17" t="n">
         <v>4.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AC17" t="n">
         <v>2.2</v>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2733,22 +2733,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>2.43</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
         <v>1.27</v>
@@ -2778,16 +2778,16 @@
         <v>2.37</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="AB18" t="n">
         <v>1.52</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AI18" t="n">
         <v>1.73</v>
@@ -2862,31 +2862,31 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="M19" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>3.68</v>
+        <v>4.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="P19" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>3.12</v>
       </c>
       <c r="U19" t="n">
         <v>1.29</v>
@@ -2898,22 +2898,22 @@
         <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
         <v>1.68</v>
@@ -2932,7 +2932,7 @@
         <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="P20" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.86</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
         <v>1.55</v>
@@ -3018,34 +3018,34 @@
         <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="V20" t="n">
         <v>1.07</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X20" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AA20" t="n">
         <v>5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
         <v>2.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="M21" t="n">
-        <v>3.26</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>3.01</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
         <v>2.67</v>
@@ -3162,7 +3162,7 @@
         <v>1.95</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AA21" t="n">
         <v>3.34</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,28 +1056,28 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.53</v>
+        <v>2.35</v>
       </c>
       <c r="P5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="R5" t="n">
         <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="T5" t="n">
         <v>2.62</v>
@@ -1089,28 +1089,28 @@
         <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X5" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="AB5" t="n">
         <v>1.28</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,28 +1185,28 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="M6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.2</v>
       </c>
-      <c r="N6" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O6" t="n">
-        <v>2.35</v>
+        <v>2.72</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="R6" t="n">
         <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="T6" t="n">
         <v>2.62</v>
@@ -1215,31 +1215,31 @@
         <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="M7" t="n">
         <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="P7" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
         <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
         <v>2.62</v>
@@ -1344,47 +1344,47 @@
         <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
         <v>3.1</v>
@@ -1710,25 +1710,25 @@
         <v>2.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q10" t="n">
         <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V10" t="n">
         <v>1.02</v>
@@ -1737,19 +1737,19 @@
         <v>1.35</v>
       </c>
       <c r="X10" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Y10" t="n">
         <v>2.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AC10" t="n">
         <v>1.91</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,77 +2217,77 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>2.82</v>
+        <v>3.95</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.84</v>
+        <v>2.18</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
-        <v>3.95</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
         <v>1.21</v>
       </c>
-      <c r="V14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="M16" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T16" t="n">
         <v>3.95</v>
       </c>
-      <c r="N16" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.72</v>
-      </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>1.23</v>
+        <v>1.63</v>
       </c>
       <c r="X16" t="n">
-        <v>3.42</v>
+        <v>2.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.86</v>
+        <v>2.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,28 +2604,28 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>4.46</v>
       </c>
       <c r="O17" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.6</v>
+        <v>4.32</v>
       </c>
       <c r="R17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S17" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
         <v>3.6</v>
@@ -2643,7 +2643,7 @@
         <v>2.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.67</v>
+        <v>2.55</v>
       </c>
       <c r="Z17" t="n">
         <v>1.4</v>
@@ -2652,13 +2652,13 @@
         <v>4.9</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AC17" t="n">
         <v>2.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         <v>1.4</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>2.4</v>
+        <v>4.05</v>
       </c>
       <c r="O18" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="P18" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>3.12</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="X18" t="n">
-        <v>4.3</v>
+        <v>2.63</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>2.33</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.37</v>
+        <v>1.48</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.02</v>
+        <v>4.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.63</v>
+        <v>1.68</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.07</v>
+        <v>2.34</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="T19" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="X19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD19" t="n">
         <v>2.63</v>
       </c>
-      <c r="Y19" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>3.01</v>
       </c>
       <c r="O20" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="P20" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>4.03</v>
       </c>
       <c r="R20" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="U20" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="X20" t="n">
-        <v>2.38</v>
+        <v>3.14</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.45</v>
+        <v>1.94</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>5</v>
+        <v>3.34</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>1.94</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>4.41</v>
       </c>
       <c r="O21" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="S21" t="n">
-        <v>2.76</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
-        <v>2.84</v>
+        <v>3.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="W21" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="X21" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.95</v>
+        <v>2.45</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.75</v>
+        <v>1.42</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.76</v>
+        <v>2.31</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.94</v>
+        <v>1.57</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,22 +669,22 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>4.22</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>8.460000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
@@ -699,31 +699,31 @@
         <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X2" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.8</v>
+        <v>3.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.81</v>
+        <v>3.19</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -798,28 +798,28 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>5.38</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
         <v>2.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
         <v>6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="T3" t="n">
         <v>3.3</v>
@@ -837,7 +837,7 @@
         <v>2.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="Z3" t="n">
         <v>1.55</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N4" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.32</v>
       </c>
-      <c r="M4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="N4" t="n">
-        <v>7</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X4" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.22</v>
+        <v>2.87</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.84</v>
+        <v>2.13</v>
       </c>
       <c r="M5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N5" t="n">
         <v>3.2</v>
       </c>
-      <c r="N5" t="n">
-        <v>4.2</v>
-      </c>
       <c r="O5" t="n">
-        <v>2.35</v>
+        <v>3.01</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.5</v>
+        <v>3.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="T5" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.86</v>
+        <v>1.46</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,28 +1185,28 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.1</v>
+        <v>1.82</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="P6" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="T6" t="n">
         <v>2.62</v>
@@ -1215,47 +1215,47 @@
         <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
         <v>2.53</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
         <v>4.2</v>
@@ -1347,13 +1347,13 @@
         <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="X7" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Z7" t="n">
         <v>1.85</v>
@@ -1362,13 +1362,13 @@
         <v>2.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1443,22 +1443,22 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>2.93</v>
+        <v>2.95</v>
       </c>
       <c r="N8" t="n">
-        <v>3.77</v>
+        <v>4.15</v>
       </c>
       <c r="O8" t="n">
         <v>2.94</v>
       </c>
       <c r="P8" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.65</v>
+        <v>4.97</v>
       </c>
       <c r="R8" t="n">
         <v>1.63</v>
@@ -1476,16 +1476,16 @@
         <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="X8" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.83</v>
+        <v>2.48</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AA8" t="n">
         <v>5.35</v>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.72</v>
+        <v>2.1</v>
       </c>
       <c r="M9" t="n">
         <v>2.8</v>
       </c>
       <c r="N9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O9" t="n">
         <v>2.9</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.4</v>
-      </c>
       <c r="P9" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
         <v>2.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X9" t="n">
         <v>2.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="M10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y10" t="n">
         <v>3.1</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.18</v>
-      </c>
       <c r="Z10" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M11" t="n">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="N11" t="n">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="P11" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="Q11" t="n">
         <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="X11" t="n">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.59</v>
+        <v>2.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="P13" t="n">
         <v>1.83</v>
@@ -2109,10 +2109,10 @@
         <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U13" t="n">
         <v>1.22</v>
@@ -2121,19 +2121,19 @@
         <v>1.14</v>
       </c>
       <c r="W13" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X13" t="n">
         <v>2.2</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Z13" t="n">
         <v>1.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.65</v>
+        <v>5.5</v>
       </c>
       <c r="AB13" t="n">
         <v>1.11</v>
@@ -2142,7 +2142,7 @@
         <v>2.37</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>2.36</v>
       </c>
       <c r="M14" t="n">
-        <v>3.95</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>5.4</v>
+        <v>2.87</v>
       </c>
       <c r="O14" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.29</v>
+        <v>1.72</v>
       </c>
       <c r="X14" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.91</v>
+        <v>3.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.78</v>
+        <v>1.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.28</v>
+        <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.76</v>
+        <v>1.48</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.36</v>
+        <v>1.55</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>2.87</v>
+        <v>5.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>2.18</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.67</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="T15" t="n">
-        <v>4.45</v>
+        <v>2.75</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.73</v>
+        <v>1.29</v>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.2</v>
+        <v>1.91</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.8</v>
+        <v>3.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2475,16 +2475,16 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="M16" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
         <v>2.82</v>
-      </c>
-      <c r="N16" t="n">
-        <v>4</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.84</v>
       </c>
       <c r="P16" t="n">
         <v>1.8</v>
@@ -2496,40 +2496,40 @@
         <v>1.62</v>
       </c>
       <c r="S16" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="T16" t="n">
         <v>3.95</v>
       </c>
       <c r="U16" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
         <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Y16" t="n">
         <v>3</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AA16" t="n">
         <v>6</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>1.36</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,62 +2733,62 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>4.05</v>
+        <v>2.4</v>
       </c>
       <c r="O18" t="n">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>3.12</v>
+        <v>2.1</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="V18" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.44</v>
+        <v>1.15</v>
       </c>
       <c r="X18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD18" t="n">
         <v>2.63</v>
       </c>
-      <c r="Y18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AE18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.34</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>4.05</v>
       </c>
       <c r="O19" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="P19" t="n">
-        <v>2.36</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>3.12</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="X19" t="n">
-        <v>4.3</v>
+        <v>2.63</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.53</v>
+        <v>2.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.37</v>
+        <v>1.48</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.02</v>
+        <v>4.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>1.18</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.63</v>
+        <v>1.68</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,28 +669,28 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="P2" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
         <v>3.1</v>
@@ -699,31 +699,31 @@
         <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
         <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.19</v>
+        <v>2.87</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,28 +927,28 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="O4" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="P4" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="R4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="T4" t="n">
         <v>3.1</v>
@@ -957,31 +957,31 @@
         <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X4" t="n">
         <v>2.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.87</v>
+        <v>3.19</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,43 +1056,43 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>3.01</v>
+        <v>2.53</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T5" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="U5" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="Y5" t="n">
         <v>1.85</v>
@@ -1101,32 +1101,32 @@
         <v>1.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC5" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.46</v>
+        <v>1.83</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,43 +1314,43 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.53</v>
+        <v>3.01</v>
       </c>
       <c r="P7" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>3.52</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T7" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="Y7" t="n">
         <v>1.85</v>
@@ -1359,16 +1359,16 @@
         <v>1.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M9" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="N9" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P9" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC9" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC11" t="n">
         <v>2.15</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>2.08</v>
       </c>
       <c r="M15" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.12</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="T15" t="n">
         <v>3.95</v>
       </c>
-      <c r="N15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.75</v>
-      </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="X15" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.91</v>
+        <v>3</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.12</v>
+        <v>1.58</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.08</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>2.76</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.82</v>
+        <v>2.18</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="S16" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="T16" t="n">
-        <v>3.95</v>
+        <v>2.75</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2</v>
+        <v>1.38</v>
       </c>
       <c r="V16" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="Y16" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="AA16" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.58</v>
+        <v>2.12</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
         <v>3.7</v>
@@ -2745,7 +2745,7 @@
         <v>2.43</v>
       </c>
       <c r="P18" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q18" t="n">
         <v>3.3</v>
@@ -2757,31 +2757,31 @@
         <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
       </c>
       <c r="W18" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X18" t="n">
         <v>4.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="AA18" t="n">
         <v>2.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
         <v>1.4</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,37 +669,37 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="P2" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.8</v>
+        <v>9.9</v>
       </c>
       <c r="R2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="U2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
         <v>1.38</v>
@@ -708,22 +708,22 @@
         <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.87</v>
+        <v>3.19</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -810,19 +810,19 @@
         <v>2.37</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="U3" t="n">
         <v>1.26</v>
@@ -843,13 +843,13 @@
         <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AB3" t="n">
         <v>1.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AD3" t="n">
         <v>1.58</v>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,22 +927,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="P4" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="R4" t="n">
         <v>1.44</v>
@@ -957,31 +957,31 @@
         <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.74</v>
+        <v>4.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.19</v>
+        <v>2.81</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,43 +1056,43 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="M5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.53</v>
+        <v>2.95</v>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
         <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X5" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="Y5" t="n">
         <v>1.85</v>
@@ -1101,16 +1101,16 @@
         <v>1.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AB5" t="n">
         <v>1.33</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1194,34 +1194,34 @@
         <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="P6" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="R6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U6" t="n">
         <v>1.38</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="X6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="Y6" t="n">
         <v>1.85</v>
@@ -1233,13 +1233,13 @@
         <v>3.08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,43 +1314,43 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.13</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>3.01</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.52</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.38</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.39</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="Y7" t="n">
         <v>1.85</v>
@@ -1359,32 +1359,32 @@
         <v>1.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="AB7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
         <v>1.3</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AH7" t="n">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1455,10 +1455,10 @@
         <v>2.94</v>
       </c>
       <c r="P8" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.97</v>
+        <v>4.65</v>
       </c>
       <c r="R8" t="n">
         <v>1.63</v>
@@ -1473,7 +1473,7 @@
         <v>1.21</v>
       </c>
       <c r="V8" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
         <v>1.55</v>
@@ -1494,10 +1494,10 @@
         <v>1.09</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AH8" t="n">
         <v>1.69</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="N9" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC9" t="n">
         <v>2.15</v>
       </c>
-      <c r="M9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AD9" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1701,28 +1701,28 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="M10" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="T10" t="n">
         <v>4</v>
@@ -1731,31 +1731,31 @@
         <v>1.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X10" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>3.11</v>
       </c>
       <c r="N11" t="n">
-        <v>3.6</v>
+        <v>3.27</v>
       </c>
       <c r="O11" t="n">
-        <v>2.9</v>
+        <v>2.68</v>
       </c>
       <c r="P11" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="R11" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="T11" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.55</v>
       </c>
-      <c r="X11" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AA11" t="n">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O12" t="n">
         <v>2.45</v>
@@ -1977,43 +1977,43 @@
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S12" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="T12" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W12" t="n">
         <v>1.42</v>
       </c>
       <c r="X12" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>3.77</v>
       </c>
       <c r="O13" t="n">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S13" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="T13" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="U13" t="n">
         <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="W13" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="X13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AA13" t="n">
         <v>5.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH13" t="n">
         <v>1.61</v>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45908.66666666666</v>
+        <v>45908.75</v>
       </c>
     </row>
     <row r="14">
@@ -2217,25 +2217,25 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
         <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>2.87</v>
+        <v>2.97</v>
       </c>
       <c r="O14" t="n">
         <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
         <v>2.15</v>
@@ -2250,16 +2250,16 @@
         <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AA14" t="n">
         <v>6.8</v>
@@ -2268,10 +2268,10 @@
         <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2346,58 +2346,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="M15" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="P15" t="n">
         <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
         <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="T15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
         <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X15" t="n">
         <v>2.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>6</v>
+        <v>6.56</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
         <v>1.5</v>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2484,7 +2484,7 @@
         <v>5.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="P16" t="n">
         <v>2.2</v>
@@ -2493,37 +2493,37 @@
         <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="X16" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="AA16" t="n">
         <v>3.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
         <v>1.93</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,55 +2604,55 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.14</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>2.89</v>
+        <v>2.92</v>
       </c>
       <c r="N17" t="n">
-        <v>4.46</v>
+        <v>3.67</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="P17" t="n">
         <v>1.86</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.32</v>
+        <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="S17" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="T17" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="X17" t="n">
         <v>2.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.9</v>
+        <v>5.45</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AC17" t="n">
         <v>2.2</v>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="O19" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.2</v>
+        <v>4.79</v>
       </c>
       <c r="R19" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X19" t="n">
         <v>2.5</v>
       </c>
-      <c r="T19" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.63</v>
-      </c>
       <c r="Y19" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="AA19" t="n">
         <v>4.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AI19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="M20" t="n">
-        <v>3.26</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3.01</v>
+        <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.03</v>
+        <v>4.5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>2.76</v>
+        <v>2.25</v>
       </c>
       <c r="T20" t="n">
-        <v>2.84</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W20" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="X20" t="n">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.94</v>
+        <v>2.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.8</v>
+        <v>1.48</v>
       </c>
       <c r="AA20" t="n">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
         <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M21" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>4.41</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA21" t="n">
         <v>3.6</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.31</v>
+        <v>1.85</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="P2" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.9</v>
+        <v>7.8</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="T2" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.33</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.38</v>
-      </c>
       <c r="X2" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.72</v>
+        <v>4.03</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.19</v>
+        <v>2.81</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,43 +798,43 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="O3" t="n">
-        <v>2.37</v>
+        <v>1.86</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>2.17</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.95</v>
+        <v>9.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="T3" t="n">
-        <v>3.48</v>
+        <v>3.24</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="Y3" t="n">
         <v>2.3</v>
@@ -843,16 +843,16 @@
         <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.5</v>
+        <v>3.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.16</v>
+        <v>3.19</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.96</v>
+        <v>2.37</v>
       </c>
       <c r="P4" t="n">
-        <v>2.29</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.8</v>
+        <v>5.95</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.03</v>
+        <v>4.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.81</v>
+        <v>2.16</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="M9" t="n">
-        <v>2.81</v>
+        <v>3.11</v>
       </c>
       <c r="N9" t="n">
-        <v>3.41</v>
+        <v>3.27</v>
       </c>
       <c r="O9" t="n">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.7</v>
+        <v>4.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="S9" t="n">
-        <v>2.37</v>
+        <v>2.65</v>
       </c>
       <c r="T9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,37 +1701,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="M10" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>3.41</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>2.59</v>
       </c>
       <c r="P10" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U10" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="W10" t="n">
         <v>1.6</v>
@@ -1740,19 +1740,19 @@
         <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="AD10" t="n">
         <v>1.57</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.03</v>
+        <v>2.44</v>
       </c>
       <c r="M11" t="n">
-        <v>3.11</v>
+        <v>2.63</v>
       </c>
       <c r="N11" t="n">
-        <v>3.27</v>
+        <v>3.03</v>
       </c>
       <c r="O11" t="n">
-        <v>2.68</v>
+        <v>3.58</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.73</v>
+        <v>1.35</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="M15" t="n">
-        <v>2.78</v>
+        <v>3.95</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="O15" t="n">
-        <v>2.97</v>
+        <v>2.16</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
         <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>2.11</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="V15" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="X15" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.04</v>
+        <v>1.87</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.56</v>
+        <v>3.25</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="M16" t="n">
-        <v>3.95</v>
+        <v>2.78</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="O16" t="n">
-        <v>2.16</v>
+        <v>2.97</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
         <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="S16" t="n">
-        <v>2.72</v>
+        <v>2.11</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W16" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="X16" t="n">
-        <v>3.35</v>
+        <v>2.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.87</v>
+        <v>3.04</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.25</v>
+        <v>6.56</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.4</v>
       </c>
-      <c r="O18" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="T18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X18" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X18" t="n">
-        <v>4.3</v>
-      </c>
       <c r="Y18" t="n">
-        <v>1.41</v>
+        <v>2.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.29</v>
+        <v>1.52</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.02</v>
+        <v>4.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="M19" t="n">
-        <v>3.04</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>3.68</v>
+        <v>2.52</v>
       </c>
       <c r="O19" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.79</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.5</v>
       </c>
-      <c r="S19" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC19" t="n">
+      <c r="AI19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N2" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="P2" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.8</v>
+        <v>9.9</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="U2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.03</v>
+        <v>3.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.81</v>
+        <v>3.19</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,43 +798,43 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.86</v>
+        <v>2.37</v>
       </c>
       <c r="P3" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.9</v>
+        <v>5.95</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S3" t="n">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="T3" t="n">
-        <v>3.24</v>
+        <v>3.48</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X3" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="Y3" t="n">
         <v>2.3</v>
@@ -843,16 +843,16 @@
         <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.72</v>
+        <v>4.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.19</v>
+        <v>2.16</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.37</v>
+        <v>1.96</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.95</v>
+        <v>7.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="T4" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W4" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="X4" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.5</v>
+        <v>4.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.16</v>
+        <v>2.81</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,43 +1056,43 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.3</v>
+        <v>4.35</v>
       </c>
       <c r="R5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.38</v>
       </c>
-      <c r="S5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X5" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="Y5" t="n">
         <v>1.85</v>
@@ -1101,16 +1101,16 @@
         <v>1.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,28 +1185,28 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="M6" t="n">
         <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="O6" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S6" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="T6" t="n">
         <v>2.72</v>
@@ -1215,13 +1215,13 @@
         <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X6" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Y6" t="n">
         <v>1.85</v>
@@ -1230,16 +1230,16 @@
         <v>1.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,43 +1314,43 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S7" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X7" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="Y7" t="n">
         <v>1.85</v>
@@ -1359,16 +1359,16 @@
         <v>1.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.03</v>
+        <v>2.12</v>
       </c>
       <c r="M9" t="n">
-        <v>3.11</v>
+        <v>2.81</v>
       </c>
       <c r="N9" t="n">
-        <v>3.27</v>
+        <v>3.41</v>
       </c>
       <c r="O9" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.33</v>
+        <v>4.7</v>
       </c>
       <c r="R9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z9" t="n">
         <v>1.4</v>
       </c>
-      <c r="S9" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AA9" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,37 +1701,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="M10" t="n">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="N10" t="n">
-        <v>3.41</v>
+        <v>3.03</v>
       </c>
       <c r="O10" t="n">
-        <v>2.59</v>
+        <v>3.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="T10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
         <v>1.6</v>
@@ -1740,19 +1740,19 @@
         <v>2.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AD10" t="n">
         <v>1.57</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.56</v>
+        <v>1.35</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,77 +1830,77 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.44</v>
+        <v>2.03</v>
       </c>
       <c r="M11" t="n">
-        <v>2.63</v>
+        <v>3.11</v>
       </c>
       <c r="N11" t="n">
-        <v>3.03</v>
+        <v>3.27</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58</v>
+        <v>2.68</v>
       </c>
       <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.73</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>4</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>3.7</v>
       </c>
       <c r="N18" t="n">
-        <v>3.68</v>
+        <v>2.52</v>
       </c>
       <c r="O18" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.79</v>
+        <v>3.3</v>
       </c>
       <c r="R18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.5</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC18" t="n">
+      <c r="AI18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ18" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.04</v>
       </c>
       <c r="N19" t="n">
-        <v>2.52</v>
+        <v>3.68</v>
       </c>
       <c r="O19" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="P19" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>4.79</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC19" t="n">
         <v>2.1</v>
       </c>
-      <c r="U19" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AD19" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="O3" t="n">
-        <v>2.37</v>
+        <v>1.96</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>2.29</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.95</v>
+        <v>7.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="T3" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.5</v>
+        <v>4.03</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.16</v>
+        <v>2.81</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N4" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.96</v>
+        <v>2.37</v>
       </c>
       <c r="P4" t="n">
-        <v>2.29</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.8</v>
+        <v>5.95</v>
       </c>
       <c r="R4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S4" t="n">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>3.48</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="X4" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.03</v>
+        <v>4.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.81</v>
+        <v>2.16</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,28 +1056,28 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="M5" t="n">
         <v>3.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="O5" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S5" t="n">
-        <v>2.85</v>
+        <v>2.89</v>
       </c>
       <c r="T5" t="n">
         <v>2.72</v>
@@ -1086,13 +1086,13 @@
         <v>1.38</v>
       </c>
       <c r="V5" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Y5" t="n">
         <v>1.85</v>
@@ -1101,16 +1101,16 @@
         <v>1.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,43 +1185,43 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.95</v>
+        <v>2.13</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="P6" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X6" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="Y6" t="n">
         <v>1.85</v>
@@ -1230,16 +1230,16 @@
         <v>1.85</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,43 +1314,43 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>2.35</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>4.35</v>
       </c>
       <c r="R7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="U7" t="n">
         <v>1.38</v>
       </c>
-      <c r="S7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W7" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="Y7" t="n">
         <v>1.85</v>
@@ -1359,16 +1359,16 @@
         <v>1.85</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.53</v>
+        <v>1.86</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Arsenal de Sarandí</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M8" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="N8" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="O8" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="P8" t="n">
         <v>1.83</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.65</v>
+        <v>4.92</v>
       </c>
       <c r="R8" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="T8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W8" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.48</v>
+        <v>2.59</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.35</v>
+        <v>5.1</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45908.5625</v>
+        <v>45908.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Arsenal de Sarandí</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1572,61 +1572,61 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="N9" t="n">
-        <v>3.41</v>
+        <v>4.15</v>
       </c>
       <c r="O9" t="n">
-        <v>2.59</v>
+        <v>2.94</v>
       </c>
       <c r="P9" t="n">
         <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="S9" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="V9" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="X9" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.1</v>
+        <v>5.35</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.56</v>
+        <v>1.69</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45908.625</v>
+        <v>45908.5625</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,77 +1701,77 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.44</v>
+        <v>2.03</v>
       </c>
       <c r="M10" t="n">
-        <v>2.63</v>
+        <v>3.11</v>
       </c>
       <c r="N10" t="n">
-        <v>3.03</v>
+        <v>3.27</v>
       </c>
       <c r="O10" t="n">
-        <v>3.58</v>
+        <v>2.68</v>
       </c>
       <c r="P10" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH10" t="n">
         <v>1.73</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T10" t="n">
-        <v>4</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.35</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.03</v>
+        <v>2.52</v>
       </c>
       <c r="M11" t="n">
-        <v>3.11</v>
+        <v>2.72</v>
       </c>
       <c r="N11" t="n">
-        <v>3.27</v>
+        <v>2.76</v>
       </c>
       <c r="O11" t="n">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>2.18</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="M13" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="N13" t="n">
-        <v>3.77</v>
+        <v>4.06</v>
       </c>
       <c r="O13" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="S13" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="T13" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.11</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.12</v>
       </c>
       <c r="AC13" t="n">
         <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>1.33</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2226,40 +2226,40 @@
         <v>2.97</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P14" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="R14" t="n">
         <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="T14" t="n">
         <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="V14" t="n">
         <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="X14" t="n">
-        <v>2.07</v>
+        <v>2.17</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.09</v>
+        <v>3.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AA14" t="n">
         <v>6.8</v>
@@ -2268,10 +2268,10 @@
         <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2310,22 +2310,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.95</v>
+        <v>2.76</v>
       </c>
       <c r="N15" t="n">
-        <v>5.4</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
-        <v>2.16</v>
+        <v>3.43</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.69</v>
       </c>
       <c r="S15" t="n">
-        <v>2.72</v>
+        <v>2.15</v>
       </c>
       <c r="T15" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="X15" t="n">
-        <v>3.35</v>
+        <v>2.1</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.87</v>
+        <v>1.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.25</v>
+        <v>6.79</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="M16" t="n">
-        <v>2.78</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="O16" t="n">
-        <v>2.97</v>
+        <v>2.16</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
         <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.11</v>
+        <v>2.72</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="X16" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="Y16" t="n">
-        <v>3.04</v>
+        <v>1.87</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.56</v>
+        <v>3.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.68</v>
+        <v>2.2</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
         <v>2.52</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="P18" t="n">
         <v>2.32</v>
@@ -2751,16 +2751,16 @@
         <v>3.3</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V18" t="n">
         <v>1.01</v>
@@ -2772,7 +2772,7 @@
         <v>5.3</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="Z18" t="n">
         <v>2.37</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AI18" t="n">
         <v>1.73</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -665,7 +665,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -678,25 +678,25 @@
         <v>5.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="P2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.9</v>
+        <v>7.3</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
       </c>
       <c r="S2" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V2" t="n">
         <v>1.01</v>
@@ -714,20 +714,20 @@
         <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -739,7 +739,7 @@
         <v>1.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.19</v>
+        <v>3.08</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,103 +772,103 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="N3" t="n">
-        <v>6.9</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.96</v>
+        <v>2.39</v>
       </c>
       <c r="P3" t="n">
-        <v>2.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.8</v>
+        <v>6.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X3" t="n">
         <v>2.59</v>
       </c>
-      <c r="T3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.84</v>
-      </c>
       <c r="Y3" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.03</v>
+        <v>4.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['21', '36']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.81</v>
+        <v>2.21</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,103 +901,103 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="O4" t="n">
-        <v>2.37</v>
+        <v>1.88</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.95</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="T4" t="n">
-        <v>3.48</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="V4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
         <v>1.04</v>
       </c>
-      <c r="W4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AH4" t="n">
-        <v>2.16</v>
+        <v>3.03</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,61 +1056,61 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="M5" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="N5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q5" t="n">
         <v>3.4</v>
       </c>
-      <c r="N5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>4</v>
-      </c>
       <c r="R5" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="U5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X5" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="Z5" t="n">
         <v>1.85</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,77 +1185,77 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="O6" t="n">
-        <v>2.95</v>
+        <v>2.5</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.3</v>
+        <v>4.35</v>
       </c>
       <c r="R6" t="n">
         <v>1.38</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="W6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1.25</v>
       </c>
-      <c r="X6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="M7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X7" t="n">
         <v>3.4</v>
       </c>
-      <c r="N7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3.35</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.08</v>
+        <v>2.95</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1443,34 +1443,34 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>2.96</v>
+        <v>2.73</v>
       </c>
       <c r="N8" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="O8" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q8" t="n">
-        <v>4.92</v>
+        <v>4.98</v>
       </c>
       <c r="R8" t="n">
         <v>1.6</v>
       </c>
       <c r="S8" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="T8" t="n">
         <v>3.6</v>
       </c>
       <c r="U8" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="V8" t="n">
         <v>1.12</v>
@@ -1479,7 +1479,7 @@
         <v>1.6</v>
       </c>
       <c r="X8" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="Y8" t="n">
         <v>2.59</v>
@@ -1488,7 +1488,7 @@
         <v>1.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="AB8" t="n">
         <v>1.13</v>
@@ -1497,7 +1497,7 @@
         <v>2.15</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1572,28 +1572,28 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="M9" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>4.15</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
         <v>2.94</v>
       </c>
       <c r="P9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.65</v>
+        <v>4.35</v>
       </c>
       <c r="R9" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="T9" t="n">
         <v>3.75</v>
@@ -1605,28 +1605,28 @@
         <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="X9" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.48</v>
+        <v>2.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.35</v>
+        <v>5.15</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
@@ -1713,31 +1713,31 @@
         <v>2.68</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V10" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="W10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X10" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="Y10" t="n">
         <v>2.3</v>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1830,22 +1830,22 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="M11" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="N11" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
         <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
         <v>1.62</v>
@@ -1854,37 +1854,37 @@
         <v>2.2</v>
       </c>
       <c r="T11" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
         <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AC11" t="n">
         <v>2.23</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="M12" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
         <v>4.6</v>
@@ -1977,16 +1977,16 @@
         <v>5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S12" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
         <v>3.28</v>
       </c>
       <c r="U12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
         <v>1.08</v>
@@ -1995,25 +1995,25 @@
         <v>1.42</v>
       </c>
       <c r="X12" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AB12" t="n">
         <v>1.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2100,10 +2100,10 @@
         <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="R13" t="n">
         <v>1.57</v>
@@ -2115,16 +2115,16 @@
         <v>4</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W13" t="n">
         <v>1.6</v>
       </c>
       <c r="X13" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="Y13" t="n">
         <v>2.75</v>
@@ -2133,7 +2133,7 @@
         <v>1.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="AB13" t="n">
         <v>1.11</v>
@@ -2142,7 +2142,7 @@
         <v>2.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AH13" t="n">
         <v>1.67</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="M14" t="n">
-        <v>2.87</v>
+        <v>3.55</v>
       </c>
       <c r="N14" t="n">
-        <v>2.97</v>
+        <v>4.9</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>2.1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.15</v>
+        <v>5</v>
       </c>
       <c r="R14" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="T14" t="n">
-        <v>4.33</v>
+        <v>2.67</v>
       </c>
       <c r="U14" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="V14" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>1.62</v>
+        <v>1.22</v>
       </c>
       <c r="X14" t="n">
-        <v>2.17</v>
+        <v>3.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.14</v>
+        <v>1.91</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.8</v>
+        <v>3.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.45</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.42</v>
+        <v>2.38</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,31 +2346,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>2.97</v>
       </c>
       <c r="O15" t="n">
-        <v>3.43</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="R15" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U15" t="n">
         <v>1.2</v>
@@ -2379,28 +2379,28 @@
         <v>1.15</v>
       </c>
       <c r="W15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.79</v>
+        <v>6.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC15" t="n">
         <v>2.45</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2413,10 +2413,10 @@
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.55</v>
+        <v>2.37</v>
       </c>
       <c r="M16" t="n">
-        <v>3.95</v>
+        <v>2.76</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>3.65</v>
       </c>
       <c r="O16" t="n">
-        <v>2.16</v>
+        <v>3.5</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="S16" t="n">
-        <v>2.72</v>
+        <v>2.15</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W16" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="X16" t="n">
-        <v>3.35</v>
+        <v>2.12</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.25</v>
+        <v>7.05</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>3.75</v>
       </c>
       <c r="U17" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
@@ -2652,7 +2652,7 @@
         <v>5.45</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AC17" t="n">
         <v>2.2</v>
@@ -2674,7 +2674,7 @@
         <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.32</v>
+        <v>1.93</v>
       </c>
       <c r="M18" t="n">
-        <v>3.7</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>2.52</v>
+        <v>3.68</v>
       </c>
       <c r="O18" t="n">
         <v>2.62</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.3</v>
+        <v>4.79</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>3.34</v>
       </c>
       <c r="U18" t="n">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="V18" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W18" t="n">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="X18" t="n">
-        <v>5.3</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>2.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.37</v>
+        <v>1.52</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.4</v>
+        <v>2.07</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.63</v>
+        <v>1.67</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,61 +2862,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="M19" t="n">
-        <v>3.04</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>3.68</v>
+        <v>2.52</v>
       </c>
       <c r="O19" t="n">
         <v>2.62</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>2.32</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.79</v>
+        <v>3.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="T19" t="n">
-        <v>3.34</v>
+        <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="V19" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>5.3</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.35</v>
+        <v>1.53</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.52</v>
+        <v>2.37</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.67</v>
+        <v>2.63</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
@@ -2932,13 +2932,13 @@
         <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45908.83333333334</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="U20" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="W20" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="X20" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,77 +3120,77 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q21" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="X21" t="n">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.95</v>
+        <v>2.37</v>
       </c>
       <c r="Z21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.67</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>

--- a/jogos_2025-09-08.xlsx
+++ b/jogos_2025-09-08.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,43 +669,43 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="M2" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N2" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.88</v>
+        <v>2.39</v>
       </c>
       <c r="P2" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S2" t="n">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="T2" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W2" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X2" t="n">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="Y2" t="n">
         <v>2.3</v>
@@ -714,32 +714,32 @@
         <v>1.55</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>['21', '36']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.08</v>
+        <v>2.21</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,22 +772,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -798,77 +798,77 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>6.9</v>
       </c>
       <c r="O3" t="n">
-        <v>2.39</v>
+        <v>1.88</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>2.32</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="R3" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="T3" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['7']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['44']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.04</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['21', '36']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AH3" t="n">
-        <v>2.21</v>
+        <v>3.03</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -901,25 +901,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,77 +927,77 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N4" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="O4" t="n">
         <v>1.88</v>
       </c>
       <c r="P4" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="R4" t="n">
         <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="T4" t="n">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U4" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X4" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['7']</t>
+          <t>['51']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['44']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="AH4" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1039,20 +1039,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1114,12 +1114,12 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27', '43', '82', '90+3']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AG5" t="n">
@@ -1168,20 +1168,20 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1297,20 +1297,20 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['35', '58', '87', '90+2']</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['89', '90+5']</t>
         </is>
       </c>
       <c r="AG7" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recoleta</t>
+          <t>Alvarado</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.03</v>
+        <v>2.65</v>
       </c>
       <c r="M10" t="n">
-        <v>3.11</v>
+        <v>2.65</v>
       </c>
       <c r="N10" t="n">
-        <v>3.27</v>
+        <v>3.05</v>
       </c>
       <c r="O10" t="n">
-        <v>2.68</v>
+        <v>3.4</v>
       </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="Q10" t="n">
         <v>4.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="T10" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="V10" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="X10" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.9</v>
+        <v>2.23</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alvarado</t>
+          <t>Recoleta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.65</v>
+        <v>1.93</v>
       </c>
       <c r="M11" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.4</v>
+        <v>2.64</v>
       </c>
       <c r="P11" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="R11" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="T11" t="n">
-        <v>4.33</v>
+        <v>3.14</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="V11" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Z11" t="n">
         <v>1.57</v>
       </c>
-      <c r="X11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AA11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['53', '79']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Estudiantes Río Cuarto</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="M14" t="n">
-        <v>3.55</v>
+        <v>2.87</v>
       </c>
       <c r="N14" t="n">
-        <v>4.9</v>
+        <v>2.97</v>
       </c>
       <c r="O14" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>2.67</v>
+        <v>4.33</v>
       </c>
       <c r="U14" t="n">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="W14" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="X14" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.91</v>
+        <v>3.14</v>
       </c>
       <c r="Z14" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="AA14" t="n">
-        <v>3.25</v>
+        <v>6.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.38</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Estudiantes Río Cuarto</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,61 +2346,61 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="M15" t="n">
-        <v>2.87</v>
+        <v>2.76</v>
       </c>
       <c r="N15" t="n">
-        <v>2.97</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="R15" t="n">
         <v>1.62</v>
       </c>
       <c r="S15" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="T15" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="V15" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>6.95</v>
+        <v>7.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>1.44</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,62 +2475,62 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.37</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>2.76</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="O16" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="P16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q16" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="T16" t="n">
-        <v>4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>7.05</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>2.38</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2604,49 +2604,49 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>2.18</v>
       </c>
       <c r="M17" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.67</v>
+        <v>3.55</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="P17" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
         <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="S17" t="n">
         <v>2.27</v>
       </c>
       <c r="T17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="V17" t="n">
         <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="X17" t="n">
-        <v>2.25</v>
+        <v>2.39</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AA17" t="n">
         <v>5.45</v>
@@ -2674,7 +2674,7 @@
         <v>1.24</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
         <v>2.62</v>
@@ -2748,19 +2748,19 @@
         <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.79</v>
+        <v>4.65</v>
       </c>
       <c r="R18" t="n">
         <v>1.5</v>
       </c>
       <c r="S18" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="U18" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V18" t="n">
         <v>1.08</v>
@@ -2769,22 +2769,22 @@
         <v>1.5</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AA18" t="n">
         <v>4.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AD18" t="n">
         <v>1.67</v>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
@@ -2862,22 +2862,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.32</v>
+        <v>2.37</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="N19" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O19" t="n">
         <v>2.62</v>
       </c>
       <c r="P19" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
         <v>1.25</v>
@@ -2889,7 +2889,7 @@
         <v>2.25</v>
       </c>
       <c r="U19" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -2904,35 +2904,35 @@
         <v>1.53</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.62</v>
       </c>
       <c r="AI19" t="n">
         <v>1.73</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,62 +2991,62 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N20" t="n">
-        <v>3.3</v>
+        <v>3.76</v>
       </c>
       <c r="O20" t="n">
         <v>2.7</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="W20" t="n">
-        <v>1.28</v>
+        <v>1.47</v>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="Y20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.05</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AD20" t="n">
         <v>1.7</v>
       </c>
-      <c r="AA20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AE20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.79</v>
+        <v>2.05</v>
       </c>
       <c r="M21" t="n">
-        <v>3.04</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="P21" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U21" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AA21" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.15</v>
+        <v>1.86</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
